--- a/docs/guide/打字練習.xlsx
+++ b/docs/guide/打字練習.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\guide\Keyboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE096A0-12E6-4E10-AF86-6E2F94B5B4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56D9FA4-574F-4A7E-8578-CE2F2AFF9F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{E1B05DE5-EAD7-43D6-8DFE-DCA2C8EA1D01}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{E1B05DE5-EAD7-43D6-8DFE-DCA2C8EA1D01}"/>
   </bookViews>
   <sheets>
     <sheet name="打字練習表" sheetId="1" r:id="rId1"/>
@@ -1411,18 +1411,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1442,9 +1430,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1513,72 +1498,27 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF1F2328"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFD1D9E0"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFD1D9E0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF1F2328"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF6F8FA"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1871,13 +1811,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFD1D9E0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FFD1D9E0"/>
         </left>
@@ -1890,6 +1823,73 @@
         <bottom style="medium">
           <color rgb="FFD1D9E0"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF1F2328"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF6F8FA"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFD1D9E0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF1F2328"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFD1D9E0"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFD1D9E0"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2191,16 +2191,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{971A3371-5FE8-45DB-A094-7F6E0F3BD8E6}" name="音調表" displayName="音調表" ref="B2:H12" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{971A3371-5FE8-45DB-A094-7F6E0F3BD8E6}" name="音調表" displayName="音調表" ref="B2:H12" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="B2:H12" xr:uid="{971A3371-5FE8-45DB-A094-7F6E0F3BD8E6}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B4D78313-6049-4165-A4FA-10B4D864693B}" name="調號" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{019BE094-2A89-4F6A-9E27-FBBE3C29A023}" name="四聲八調" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{5D368C68-E5DA-41CE-99D8-401BBE9A56ED}" name="聲調按鍵" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{66C34166-F70F-45A8-8228-F7CDD2B34540}" name="Key" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{1203CFE8-BF5B-4A31-BE73-137200C48083}" name="漢字" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{04856A3F-6E55-4523-BF7B-BBE739377949}" name="台語音標" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{6E6BB8E3-8E9D-44DF-AA55-7BC23DBF0DA6}" name="按鍵輸入" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B4D78313-6049-4165-A4FA-10B4D864693B}" name="調號" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{019BE094-2A89-4F6A-9E27-FBBE3C29A023}" name="四聲八調" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{5D368C68-E5DA-41CE-99D8-401BBE9A56ED}" name="聲調按鍵" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{66C34166-F70F-45A8-8228-F7CDD2B34540}" name="Key" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{1203CFE8-BF5B-4A31-BE73-137200C48083}" name="漢字" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{04856A3F-6E55-4523-BF7B-BBE739377949}" name="台語音標" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{6E6BB8E3-8E9D-44DF-AA55-7BC23DBF0DA6}" name="按鍵輸入" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2540,31 +2540,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="20"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="49"/>
     </row>
     <row r="3" spans="2:17" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
       <c r="E3" s="9">
         <v>1</v>
       </c>
@@ -4636,7 +4636,7 @@
   <cols>
     <col min="1" max="1" width="4.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="17" style="23" customWidth="1"/>
+    <col min="3" max="3" width="17" style="19" customWidth="1"/>
     <col min="4" max="4" width="21.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1" outlineLevel="1"/>
     <col min="6" max="16" width="9" style="1"/>
@@ -4648,38 +4648,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="39" x14ac:dyDescent="0.25">
-      <c r="C1" s="21"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="2" spans="2:18" ht="39" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="20"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="2:18" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
       <c r="F3" s="9">
         <v>1</v>
       </c>
@@ -4712,7 +4712,7 @@
       <c r="B4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="27" t="s">
         <v>133</v>
       </c>
       <c r="D4" s="13" t="s">
@@ -4769,7 +4769,7 @@
       <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="28" t="s">
         <v>134</v>
       </c>
       <c r="D5" s="13" t="s">
@@ -4822,7 +4822,7 @@
       <c r="B6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="28" t="s">
         <v>135</v>
       </c>
       <c r="D6" s="13" t="s">
@@ -4873,7 +4873,7 @@
     </row>
     <row r="7" spans="2:18" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B7" s="12"/>
-      <c r="C7" s="32"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="13"/>
       <c r="E7" s="14" t="str">
         <f t="shared" si="0"/>
@@ -4922,7 +4922,7 @@
       <c r="B8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="27" t="s">
         <v>136</v>
       </c>
       <c r="D8" s="13" t="s">
@@ -4975,7 +4975,7 @@
       <c r="B9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="27" t="s">
         <v>137</v>
       </c>
       <c r="D9" s="13" t="s">
@@ -5028,7 +5028,7 @@
       <c r="B10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="27" t="s">
         <v>138</v>
       </c>
       <c r="D10" s="13" t="s">
@@ -5079,7 +5079,7 @@
     </row>
     <row r="11" spans="2:18" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B11" s="12"/>
-      <c r="C11" s="32"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="13"/>
       <c r="E11" s="14" t="str">
         <f t="shared" si="0"/>
@@ -5128,7 +5128,7 @@
       <c r="B12" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="27" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="13" t="s">
@@ -5181,7 +5181,7 @@
       <c r="B13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="27" t="s">
         <v>140</v>
       </c>
       <c r="D13" s="13" t="s">
@@ -5234,7 +5234,7 @@
       <c r="B14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="27" t="s">
         <v>141</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -5287,7 +5287,7 @@
       <c r="B15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="27" t="s">
         <v>142</v>
       </c>
       <c r="D15" s="13" t="s">
@@ -5340,7 +5340,7 @@
       <c r="B16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="27" t="s">
         <v>143</v>
       </c>
       <c r="D16" s="13" t="s">
@@ -5393,7 +5393,7 @@
       <c r="B17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="27" t="s">
         <v>144</v>
       </c>
       <c r="D17" s="13" t="s">
@@ -5446,7 +5446,7 @@
       <c r="B18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="27" t="s">
         <v>145</v>
       </c>
       <c r="D18" s="13" t="s">
@@ -5499,7 +5499,7 @@
       <c r="B19" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="32"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="13"/>
       <c r="E19" s="14" t="str">
         <f t="shared" si="0"/>
@@ -5546,7 +5546,7 @@
       <c r="B20" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="27" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="13" t="s">
@@ -5599,7 +5599,7 @@
       <c r="B21" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="27" t="s">
         <v>147</v>
       </c>
       <c r="D21" s="13" t="s">
@@ -5652,7 +5652,7 @@
       <c r="B22" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="27" t="s">
         <v>148</v>
       </c>
       <c r="D22" s="13" t="s">
@@ -5705,7 +5705,7 @@
       <c r="B23" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="27" t="s">
         <v>149</v>
       </c>
       <c r="D23" s="13" t="s">
@@ -5758,7 +5758,7 @@
       <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="27" t="s">
         <v>150</v>
       </c>
       <c r="D24" s="13" t="s">
@@ -5811,7 +5811,7 @@
       <c r="B25" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="27" t="s">
         <v>151</v>
       </c>
       <c r="D25" s="13" t="s">
@@ -5864,7 +5864,7 @@
       <c r="B26" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="27" t="s">
         <v>153</v>
       </c>
       <c r="D26" s="13" t="s">
@@ -5917,7 +5917,7 @@
       <c r="B27" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="32"/>
+      <c r="C27" s="27"/>
       <c r="D27" s="13"/>
       <c r="E27" s="14" t="str">
         <f t="shared" si="0"/>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="28" spans="2:17" ht="45.75" x14ac:dyDescent="0.25">
       <c r="B28" s="12"/>
-      <c r="C28" s="32"/>
+      <c r="C28" s="27"/>
       <c r="D28" s="13"/>
       <c r="E28" s="14" t="str">
         <f t="shared" si="0"/>
@@ -6009,7 +6009,7 @@
       <c r="B29" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="27" t="s">
         <v>154</v>
       </c>
       <c r="D29" s="13" t="s">
@@ -6062,7 +6062,7 @@
       <c r="B30" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="27" t="s">
         <v>155</v>
       </c>
       <c r="D30" s="13" t="s">
@@ -6115,7 +6115,7 @@
       <c r="B31" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="27" t="s">
         <v>140</v>
       </c>
       <c r="D31" s="13" t="s">
@@ -6168,7 +6168,7 @@
       <c r="B32" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="28" t="s">
         <v>156</v>
       </c>
       <c r="D32" s="13" t="s">
@@ -6221,7 +6221,7 @@
       <c r="B33" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="27" t="s">
         <v>157</v>
       </c>
       <c r="D33" s="13" t="s">
@@ -6274,7 +6274,7 @@
       <c r="B34" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="27" t="s">
         <v>158</v>
       </c>
       <c r="D34" s="13" t="s">
@@ -6327,7 +6327,7 @@
       <c r="B35" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="28" t="s">
         <v>159</v>
       </c>
       <c r="D35" s="13" t="s">
@@ -6380,7 +6380,7 @@
       <c r="B36" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14" t="str">
         <f t="shared" si="0"/>
@@ -6427,7 +6427,7 @@
       <c r="B37" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="27" t="s">
         <v>160</v>
       </c>
       <c r="D37" s="13" t="s">
@@ -6480,7 +6480,7 @@
       <c r="B38" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="27" t="s">
         <v>161</v>
       </c>
       <c r="D38" s="13" t="s">
@@ -6533,7 +6533,7 @@
       <c r="B39" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="27" t="s">
         <v>162</v>
       </c>
       <c r="D39" s="13" t="s">
@@ -6586,7 +6586,7 @@
       <c r="B40" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="27" t="s">
         <v>163</v>
       </c>
       <c r="D40" s="13" t="s">
@@ -6639,7 +6639,7 @@
       <c r="B41" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="27" t="s">
         <v>164</v>
       </c>
       <c r="D41" s="13" t="s">
@@ -6692,7 +6692,7 @@
       <c r="B42" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="27" t="s">
         <v>165</v>
       </c>
       <c r="D42" s="13" t="s">
@@ -6745,7 +6745,7 @@
       <c r="B43" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="27" t="s">
         <v>166</v>
       </c>
       <c r="D43" s="13" t="s">
@@ -6798,7 +6798,7 @@
       <c r="B44" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="32"/>
+      <c r="C44" s="27"/>
       <c r="D44" s="13"/>
       <c r="E44" s="14" t="str">
         <f t="shared" si="0"/>
@@ -6860,11 +6860,11 @@
   <sheetFormatPr defaultRowHeight="114" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.25" style="1" customWidth="1"/>
-    <col min="2" max="3" width="17" style="23" customWidth="1"/>
-    <col min="4" max="4" width="21.125" style="24" customWidth="1"/>
+    <col min="2" max="3" width="17" style="19" customWidth="1"/>
+    <col min="4" max="4" width="21.125" style="20" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="6" max="14" width="18.125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="2" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="2" style="43" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="16" max="16" width="12.625" style="1" customWidth="1" collapsed="1"/>
     <col min="17" max="24" width="12.625" style="1" customWidth="1"/>
     <col min="25" max="36" width="15.625" style="1" customWidth="1"/>
@@ -6872,205 +6872,205 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" ht="39" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="22" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="18" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
     </row>
     <row r="3" spans="2:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="26" t="s">
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26"/>
-      <c r="X3" s="26"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="50"/>
     </row>
     <row r="4" spans="2:26" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="28">
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="22">
         <v>1</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="22">
         <v>2</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="22">
         <v>3</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="22">
         <v>4</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="22">
         <v>5</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="22">
         <v>6</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="22">
         <v>7</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="22">
         <v>8</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="22">
         <v>9</v>
       </c>
-      <c r="O4" s="50"/>
-      <c r="P4" s="28">
+      <c r="O4" s="45"/>
+      <c r="P4" s="22">
         <v>1</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="22">
         <v>2</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="22">
         <v>3</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="22">
         <v>4</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="22">
         <v>5</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="22">
         <v>6</v>
       </c>
-      <c r="V4" s="28">
+      <c r="V4" s="22">
         <v>7</v>
       </c>
-      <c r="W4" s="28">
+      <c r="W4" s="22">
         <v>8</v>
       </c>
-      <c r="X4" s="28">
+      <c r="X4" s="22">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>IF( LEN(D5)&gt;0, LEN(D5), "")</f>
         <v>6</v>
       </c>
-      <c r="F5" s="47" t="str" cm="1">
+      <c r="F5" s="42" t="str" cm="1">
         <f t="array" ref="F5" xml:space="preserve"> IF(F$4&lt;&gt;$E5, MID($D5,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>l</v>
       </c>
-      <c r="G5" s="47" t="str" cm="1">
+      <c r="G5" s="42" t="str" cm="1">
         <f t="array" ref="G5" xml:space="preserve"> IF(G$4&lt;&gt;$E5, MID($D5,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H5" s="47" t="str" cm="1">
+      <c r="H5" s="42" t="str" cm="1">
         <f t="array" ref="H5" xml:space="preserve"> IF(H$4&lt;&gt;$E5, MID($D5,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="I5" s="47" t="str" cm="1">
+      <c r="I5" s="42" t="str" cm="1">
         <f t="array" ref="I5" xml:space="preserve"> IF(I$4&lt;&gt;$E5, MID($D5,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J5" s="47" t="str" cm="1">
+      <c r="J5" s="42" t="str" cm="1">
         <f t="array" ref="J5" xml:space="preserve"> IF(J$4&lt;&gt;$E5, MID($D5,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="K5" s="47" t="str" cm="1">
+      <c r="K5" s="42" t="str" cm="1">
         <f t="array" ref="K5" xml:space="preserve"> IF(K$4&lt;&gt;$E5, MID($D5,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="L5" s="47" t="str" cm="1">
+      <c r="L5" s="42" t="str" cm="1">
         <f t="array" ref="L5" xml:space="preserve"> IF(L$4&lt;&gt;$E5, MID($D5,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M5" s="47" t="str" cm="1">
+      <c r="M5" s="42" t="str" cm="1">
         <f t="array" ref="M5" xml:space="preserve"> IF(M$4&lt;&gt;$E5, MID($D5,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N5" s="47" t="str" cm="1">
+      <c r="N5" s="42" t="str" cm="1">
         <f t="array" ref="N5" xml:space="preserve"> IF(N$4&lt;&gt;$E5, MID($D5,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D5,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O5" s="49"/>
-      <c r="P5" s="31" t="e" vm="1">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q5" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R5" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S5" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T5" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U5" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K5,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V5" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L5,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W5" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M5,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X5" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N5,".png")), "")</f>
+      <c r="O5" s="44"/>
+      <c r="P5" s="26" t="e" vm="1">
+        <f t="shared" ref="P5:Y5" si="0" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F5,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q5" s="26" t="e" vm="2">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R5" s="26" t="e" vm="3">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S5" s="26" t="e" vm="4">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T5" s="26" t="e" vm="5">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U5" s="26" t="e" vm="6">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V5" s="26" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+      <c r="W5" s="26" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+      <c r="X5" s="26" t="str">
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Y5" s="2" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,O5,".png")), "")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="Z5" s="2" t="str">
@@ -7079,3488 +7079,3488 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="27">
-        <f t="shared" ref="E6:E45" si="0">IF( LEN(D6)&gt;0, LEN(D6), "")</f>
+      <c r="E6" s="23">
+        <f t="shared" ref="E6:E45" si="1">IF( LEN(D6)&gt;0, LEN(D6), "")</f>
         <v>5</v>
       </c>
-      <c r="F6" s="47" t="str" cm="1">
+      <c r="F6" s="42" t="str" cm="1">
         <f t="array" ref="F6" xml:space="preserve"> IF(F$4&lt;&gt;$E6, MID($D6,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G6" s="47" t="str" cm="1">
+      <c r="G6" s="42" t="str" cm="1">
         <f t="array" ref="G6" xml:space="preserve"> IF(G$4&lt;&gt;$E6, MID($D6,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="H6" s="47" t="str" cm="1">
+      <c r="H6" s="42" t="str" cm="1">
         <f t="array" ref="H6" xml:space="preserve"> IF(H$4&lt;&gt;$E6, MID($D6,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="I6" s="47" t="str" cm="1">
+      <c r="I6" s="42" t="str" cm="1">
         <f t="array" ref="I6" xml:space="preserve"> IF(I$4&lt;&gt;$E6, MID($D6,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="J6" s="47" t="str" cm="1">
+      <c r="J6" s="42" t="str" cm="1">
         <f t="array" ref="J6" xml:space="preserve"> IF(J$4&lt;&gt;$E6, MID($D6,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="K6" s="47" t="str" cm="1">
+      <c r="K6" s="42" t="str" cm="1">
         <f t="array" ref="K6" xml:space="preserve"> IF(K$4&lt;&gt;$E6, MID($D6,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L6" s="47" t="str" cm="1">
+      <c r="L6" s="42" t="str" cm="1">
         <f t="array" ref="L6" xml:space="preserve"> IF(L$4&lt;&gt;$E6, MID($D6,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M6" s="47" t="str" cm="1">
+      <c r="M6" s="42" t="str" cm="1">
         <f t="array" ref="M6" xml:space="preserve"> IF(M$4&lt;&gt;$E6, MID($D6,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N6" s="47" t="str" cm="1">
+      <c r="N6" s="42" t="str" cm="1">
         <f t="array" ref="N6" xml:space="preserve"> IF(N$4&lt;&gt;$E6, MID($D6,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D6,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O6" s="49"/>
-      <c r="P6" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F6,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q6" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G6,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R6" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H6,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S6" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I6,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T6" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J6,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U6" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K6,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V6" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L6,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W6" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M6,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X6" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N6,".png")), "")</f>
+      <c r="O6" s="44"/>
+      <c r="P6" s="26" t="e" vm="7">
+        <f t="shared" ref="P6:P45" si="2" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F6,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q6" s="26" t="e" vm="8">
+        <f t="shared" ref="Q6:Q45" si="3" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G6,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R6" s="26" t="e" vm="2">
+        <f t="shared" ref="R6:R45" si="4" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H6,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S6" s="26" t="e" vm="9">
+        <f t="shared" ref="S6:S45" si="5" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I6,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T6" s="26" t="e" vm="10">
+        <f t="shared" ref="T6:T45" si="6" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J6,".png")), "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U6" s="26" t="str">
+        <f t="shared" ref="U6:U45" ca="1" si="7" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K6,".png")), "")</f>
+        <v/>
+      </c>
+      <c r="V6" s="26" t="str">
+        <f t="shared" ref="V6:V45" ca="1" si="8" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L6,".png")), "")</f>
+        <v/>
+      </c>
+      <c r="W6" s="26" t="str">
+        <f t="shared" ref="W6:W45" ca="1" si="9" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M6,".png")), "")</f>
+        <v/>
+      </c>
+      <c r="X6" s="26" t="str">
+        <f t="shared" ref="X6:X45" ca="1" si="10" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N6,".png")), "")</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="27">
-        <f t="shared" si="0"/>
+      <c r="E7" s="23">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F7" s="47" t="str" cm="1">
+      <c r="F7" s="42" t="str" cm="1">
         <f t="array" ref="F7" xml:space="preserve"> IF(F$4&lt;&gt;$E7, MID($D7,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="G7" s="47" t="str" cm="1">
+      <c r="G7" s="42" t="str" cm="1">
         <f t="array" ref="G7" xml:space="preserve"> IF(G$4&lt;&gt;$E7, MID($D7,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H7" s="47" t="str" cm="1">
+      <c r="H7" s="42" t="str" cm="1">
         <f t="array" ref="H7" xml:space="preserve"> IF(H$4&lt;&gt;$E7, MID($D7,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="I7" s="47" t="str" cm="1">
+      <c r="I7" s="42" t="str" cm="1">
         <f t="array" ref="I7" xml:space="preserve"> IF(I$4&lt;&gt;$E7, MID($D7,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J7" s="47" t="str" cm="1">
+      <c r="J7" s="42" t="str" cm="1">
         <f t="array" ref="J7" xml:space="preserve"> IF(J$4&lt;&gt;$E7, MID($D7,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K7" s="47" t="str" cm="1">
+      <c r="K7" s="42" t="str" cm="1">
         <f t="array" ref="K7" xml:space="preserve"> IF(K$4&lt;&gt;$E7, MID($D7,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L7" s="47" t="str" cm="1">
+      <c r="L7" s="42" t="str" cm="1">
         <f t="array" ref="L7" xml:space="preserve"> IF(L$4&lt;&gt;$E7, MID($D7,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M7" s="47" t="str" cm="1">
+      <c r="M7" s="42" t="str" cm="1">
         <f t="array" ref="M7" xml:space="preserve"> IF(M$4&lt;&gt;$E7, MID($D7,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N7" s="47" t="str" cm="1">
+      <c r="N7" s="42" t="str" cm="1">
         <f t="array" ref="N7" xml:space="preserve"> IF(N$4&lt;&gt;$E7, MID($D7,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D7,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O7" s="49"/>
-      <c r="P7" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F7,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q7" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G7,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R7" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H7,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I7,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J7,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K7,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L7,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M7,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X7" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N7,".png")), "")</f>
+      <c r="O7" s="44"/>
+      <c r="P7" s="26" t="e" vm="8">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q7" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R7" s="26" t="e" vm="6">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S7" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T7" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U7" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V7" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W7" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X7" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="8" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="29"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F8" s="47" t="str" cm="1">
+      <c r="B8" s="24"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="42" t="str" cm="1">
         <f t="array" ref="F8" xml:space="preserve"> IF(F$4&lt;&gt;$E8, MID($D8,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G8" s="47" t="str" cm="1">
+      <c r="G8" s="42" t="str" cm="1">
         <f t="array" ref="G8" xml:space="preserve"> IF(G$4&lt;&gt;$E8, MID($D8,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H8" s="47" t="str" cm="1">
+      <c r="H8" s="42" t="str" cm="1">
         <f t="array" ref="H8" xml:space="preserve"> IF(H$4&lt;&gt;$E8, MID($D8,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I8" s="47" t="str" cm="1">
+      <c r="I8" s="42" t="str" cm="1">
         <f t="array" ref="I8" xml:space="preserve"> IF(I$4&lt;&gt;$E8, MID($D8,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J8" s="47" t="str" cm="1">
+      <c r="J8" s="42" t="str" cm="1">
         <f t="array" ref="J8" xml:space="preserve"> IF(J$4&lt;&gt;$E8, MID($D8,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K8" s="47" t="str" cm="1">
+      <c r="K8" s="42" t="str" cm="1">
         <f t="array" ref="K8" xml:space="preserve"> IF(K$4&lt;&gt;$E8, MID($D8,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L8" s="47" t="str" cm="1">
+      <c r="L8" s="42" t="str" cm="1">
         <f t="array" ref="L8" xml:space="preserve"> IF(L$4&lt;&gt;$E8, MID($D8,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M8" s="47" t="str" cm="1">
+      <c r="M8" s="42" t="str" cm="1">
         <f t="array" ref="M8" xml:space="preserve"> IF(M$4&lt;&gt;$E8, MID($D8,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N8" s="47" t="str" cm="1">
+      <c r="N8" s="42" t="str" cm="1">
         <f t="array" ref="N8" xml:space="preserve"> IF(N$4&lt;&gt;$E8, MID($D8,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D8,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O8" s="49"/>
-      <c r="P8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M8,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X8" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N8,".png")), "")</f>
+      <c r="O8" s="44"/>
+      <c r="P8" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q8" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R8" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S8" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T8" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U8" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V8" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W8" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X8" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="27">
-        <f t="shared" si="0"/>
+      <c r="E9" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F9" s="47" t="str" cm="1">
+      <c r="F9" s="42" t="str" cm="1">
         <f t="array" ref="F9" xml:space="preserve"> IF(F$4&lt;&gt;$E9, MID($D9,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="G9" s="47" t="str" cm="1">
+      <c r="G9" s="42" t="str" cm="1">
         <f t="array" ref="G9" xml:space="preserve"> IF(G$4&lt;&gt;$E9, MID($D9,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="H9" s="47" t="str" cm="1">
+      <c r="H9" s="42" t="str" cm="1">
         <f t="array" ref="H9" xml:space="preserve"> IF(H$4&lt;&gt;$E9, MID($D9,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="I9" s="47" t="str" cm="1">
+      <c r="I9" s="42" t="str" cm="1">
         <f t="array" ref="I9" xml:space="preserve"> IF(I$4&lt;&gt;$E9, MID($D9,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="J9" s="47" t="str" cm="1">
+      <c r="J9" s="42" t="str" cm="1">
         <f t="array" ref="J9" xml:space="preserve"> IF(J$4&lt;&gt;$E9, MID($D9,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K9" s="47" t="str" cm="1">
+      <c r="K9" s="42" t="str" cm="1">
         <f t="array" ref="K9" xml:space="preserve"> IF(K$4&lt;&gt;$E9, MID($D9,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L9" s="47" t="str" cm="1">
+      <c r="L9" s="42" t="str" cm="1">
         <f t="array" ref="L9" xml:space="preserve"> IF(L$4&lt;&gt;$E9, MID($D9,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M9" s="47" t="str" cm="1">
+      <c r="M9" s="42" t="str" cm="1">
         <f t="array" ref="M9" xml:space="preserve"> IF(M$4&lt;&gt;$E9, MID($D9,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N9" s="47" t="str" cm="1">
+      <c r="N9" s="42" t="str" cm="1">
         <f t="array" ref="N9" xml:space="preserve"> IF(N$4&lt;&gt;$E9, MID($D9,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D9,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O9" s="49"/>
-      <c r="P9" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F9,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q9" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G9,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R9" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H9,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S9" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I9,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T9" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J9,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U9" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K9,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V9" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L9,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W9" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M9,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X9" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N9,".png")), "")</f>
+      <c r="O9" s="44"/>
+      <c r="P9" s="26" t="e" vm="11">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" s="26" t="e" vm="4">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R9" s="26" t="e" vm="5">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S9" s="26" t="e" vm="6">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T9" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U9" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V9" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W9" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X9" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="27">
-        <f t="shared" si="0"/>
+      <c r="E10" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F10" s="47" t="str" cm="1">
+      <c r="F10" s="42" t="str" cm="1">
         <f t="array" ref="F10" xml:space="preserve"> IF(F$4&lt;&gt;$E10, MID($D10,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G10" s="47" t="str" cm="1">
+      <c r="G10" s="42" t="str" cm="1">
         <f t="array" ref="G10" xml:space="preserve"> IF(G$4&lt;&gt;$E10, MID($D10,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="H10" s="47" t="str" cm="1">
+      <c r="H10" s="42" t="str" cm="1">
         <f t="array" ref="H10" xml:space="preserve"> IF(H$4&lt;&gt;$E10, MID($D10,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="I10" s="47" t="str" cm="1">
+      <c r="I10" s="42" t="str" cm="1">
         <f t="array" ref="I10" xml:space="preserve"> IF(I$4&lt;&gt;$E10, MID($D10,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="J10" s="47" t="str" cm="1">
+      <c r="J10" s="42" t="str" cm="1">
         <f t="array" ref="J10" xml:space="preserve"> IF(J$4&lt;&gt;$E10, MID($D10,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K10" s="47" t="str" cm="1">
+      <c r="K10" s="42" t="str" cm="1">
         <f t="array" ref="K10" xml:space="preserve"> IF(K$4&lt;&gt;$E10, MID($D10,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L10" s="47" t="str" cm="1">
+      <c r="L10" s="42" t="str" cm="1">
         <f t="array" ref="L10" xml:space="preserve"> IF(L$4&lt;&gt;$E10, MID($D10,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M10" s="47" t="str" cm="1">
+      <c r="M10" s="42" t="str" cm="1">
         <f t="array" ref="M10" xml:space="preserve"> IF(M$4&lt;&gt;$E10, MID($D10,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N10" s="47" t="str" cm="1">
+      <c r="N10" s="42" t="str" cm="1">
         <f t="array" ref="N10" xml:space="preserve"> IF(N$4&lt;&gt;$E10, MID($D10,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D10,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O10" s="49"/>
-      <c r="P10" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F10,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q10" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G10,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R10" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H10,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S10" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I10,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T10" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J10,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U10" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K10,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V10" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L10,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W10" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M10,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X10" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N10,".png")), "")</f>
+      <c r="O10" s="44"/>
+      <c r="P10" s="26" t="e" vm="7">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q10" s="26" t="e" vm="8">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R10" s="26" t="e" vm="2">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S10" s="26" t="e" vm="10">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T10" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U10" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V10" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W10" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X10" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="27">
-        <f t="shared" si="0"/>
+      <c r="E11" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F11" s="47" t="str" cm="1">
+      <c r="F11" s="42" t="str" cm="1">
         <f t="array" ref="F11" xml:space="preserve"> IF(F$4&lt;&gt;$E11, MID($D11,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G11" s="47" t="str" cm="1">
+      <c r="G11" s="42" t="str" cm="1">
         <f t="array" ref="G11" xml:space="preserve"> IF(G$4&lt;&gt;$E11, MID($D11,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H11" s="47" t="str" cm="1">
+      <c r="H11" s="42" t="str" cm="1">
         <f t="array" ref="H11" xml:space="preserve"> IF(H$4&lt;&gt;$E11, MID($D11,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="I11" s="47" t="str" cm="1">
+      <c r="I11" s="42" t="str" cm="1">
         <f t="array" ref="I11" xml:space="preserve"> IF(I$4&lt;&gt;$E11, MID($D11,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J11" s="47" t="str" cm="1">
+      <c r="J11" s="42" t="str" cm="1">
         <f t="array" ref="J11" xml:space="preserve"> IF(J$4&lt;&gt;$E11, MID($D11,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="K11" s="47" t="str" cm="1">
+      <c r="K11" s="42" t="str" cm="1">
         <f t="array" ref="K11" xml:space="preserve"> IF(K$4&lt;&gt;$E11, MID($D11,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L11" s="47" t="str" cm="1">
+      <c r="L11" s="42" t="str" cm="1">
         <f t="array" ref="L11" xml:space="preserve"> IF(L$4&lt;&gt;$E11, MID($D11,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M11" s="47" t="str" cm="1">
+      <c r="M11" s="42" t="str" cm="1">
         <f t="array" ref="M11" xml:space="preserve"> IF(M$4&lt;&gt;$E11, MID($D11,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N11" s="47" t="str" cm="1">
+      <c r="N11" s="42" t="str" cm="1">
         <f t="array" ref="N11" xml:space="preserve"> IF(N$4&lt;&gt;$E11, MID($D11,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D11,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O11" s="49"/>
-      <c r="P11" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F11,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q11" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G11,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R11" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H11,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S11" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I11,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T11" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J11,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U11" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K11,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V11" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L11,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W11" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M11,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X11" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N11,".png")), "")</f>
+      <c r="O11" s="44"/>
+      <c r="P11" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q11" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R11" s="26" t="e" vm="3">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S11" s="26" t="e" vm="4">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T11" s="26" t="e" vm="13">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U11" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V11" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W11" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X11" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F12" s="47" t="str" cm="1">
+      <c r="B12" s="24"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F12" s="42" t="str" cm="1">
         <f t="array" ref="F12" xml:space="preserve"> IF(F$4&lt;&gt;$E12, MID($D12,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G12" s="47" t="str" cm="1">
+      <c r="G12" s="42" t="str" cm="1">
         <f t="array" ref="G12" xml:space="preserve"> IF(G$4&lt;&gt;$E12, MID($D12,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H12" s="47" t="str" cm="1">
+      <c r="H12" s="42" t="str" cm="1">
         <f t="array" ref="H12" xml:space="preserve"> IF(H$4&lt;&gt;$E12, MID($D12,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I12" s="47" t="str" cm="1">
+      <c r="I12" s="42" t="str" cm="1">
         <f t="array" ref="I12" xml:space="preserve"> IF(I$4&lt;&gt;$E12, MID($D12,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J12" s="47" t="str" cm="1">
+      <c r="J12" s="42" t="str" cm="1">
         <f t="array" ref="J12" xml:space="preserve"> IF(J$4&lt;&gt;$E12, MID($D12,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K12" s="47" t="str" cm="1">
+      <c r="K12" s="42" t="str" cm="1">
         <f t="array" ref="K12" xml:space="preserve"> IF(K$4&lt;&gt;$E12, MID($D12,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L12" s="47" t="str" cm="1">
+      <c r="L12" s="42" t="str" cm="1">
         <f t="array" ref="L12" xml:space="preserve"> IF(L$4&lt;&gt;$E12, MID($D12,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M12" s="47" t="str" cm="1">
+      <c r="M12" s="42" t="str" cm="1">
         <f t="array" ref="M12" xml:space="preserve"> IF(M$4&lt;&gt;$E12, MID($D12,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N12" s="47" t="str" cm="1">
+      <c r="N12" s="42" t="str" cm="1">
         <f t="array" ref="N12" xml:space="preserve"> IF(N$4&lt;&gt;$E12, MID($D12,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D12,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O12" s="49"/>
-      <c r="P12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M12,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X12" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N12,".png")), "")</f>
+      <c r="O12" s="44"/>
+      <c r="P12" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q12" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R12" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S12" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T12" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U12" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V12" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W12" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X12" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="27">
-        <f t="shared" si="0"/>
+      <c r="E13" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F13" s="47" t="str" cm="1">
+      <c r="F13" s="42" t="str" cm="1">
         <f t="array" ref="F13" xml:space="preserve"> IF(F$4&lt;&gt;$E13, MID($D13,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G13" s="47" t="str" cm="1">
+      <c r="G13" s="42" t="str" cm="1">
         <f t="array" ref="G13" xml:space="preserve"> IF(G$4&lt;&gt;$E13, MID($D13,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H13" s="47" t="str" cm="1">
+      <c r="H13" s="42" t="str" cm="1">
         <f t="array" ref="H13" xml:space="preserve"> IF(H$4&lt;&gt;$E13, MID($D13,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I13" s="47" t="str" cm="1">
+      <c r="I13" s="42" t="str" cm="1">
         <f t="array" ref="I13" xml:space="preserve"> IF(I$4&lt;&gt;$E13, MID($D13,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J13" s="47" t="str" cm="1">
+      <c r="J13" s="42" t="str" cm="1">
         <f t="array" ref="J13" xml:space="preserve"> IF(J$4&lt;&gt;$E13, MID($D13,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="K13" s="47" t="str" cm="1">
+      <c r="K13" s="42" t="str" cm="1">
         <f t="array" ref="K13" xml:space="preserve"> IF(K$4&lt;&gt;$E13, MID($D13,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L13" s="47" t="str" cm="1">
+      <c r="L13" s="42" t="str" cm="1">
         <f t="array" ref="L13" xml:space="preserve"> IF(L$4&lt;&gt;$E13, MID($D13,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M13" s="47" t="str" cm="1">
+      <c r="M13" s="42" t="str" cm="1">
         <f t="array" ref="M13" xml:space="preserve"> IF(M$4&lt;&gt;$E13, MID($D13,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N13" s="47" t="str" cm="1">
+      <c r="N13" s="42" t="str" cm="1">
         <f t="array" ref="N13" xml:space="preserve"> IF(N$4&lt;&gt;$E13, MID($D13,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D13,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O13" s="49"/>
-      <c r="P13" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F13,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q13" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G13,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R13" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H13,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S13" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I13,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T13" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J13,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U13" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K13,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V13" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L13,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W13" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M13,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X13" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N13,".png")), "")</f>
+      <c r="O13" s="44"/>
+      <c r="P13" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q13" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R13" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S13" s="26" t="e" vm="5">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T13" s="26" t="e" vm="6">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U13" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V13" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W13" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X13" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="27">
-        <f t="shared" si="0"/>
+      <c r="E14" s="23">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F14" s="47" t="str" cm="1">
+      <c r="F14" s="42" t="str" cm="1">
         <f t="array" ref="F14" xml:space="preserve"> IF(F$4&lt;&gt;$E14, MID($D14,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G14" s="47" t="str" cm="1">
+      <c r="G14" s="42" t="str" cm="1">
         <f t="array" ref="G14" xml:space="preserve"> IF(G$4&lt;&gt;$E14, MID($D14,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H14" s="47" t="str" cm="1">
+      <c r="H14" s="42" t="str" cm="1">
         <f t="array" ref="H14" xml:space="preserve"> IF(H$4&lt;&gt;$E14, MID($D14,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="I14" s="47" t="str" cm="1">
+      <c r="I14" s="42" t="str" cm="1">
         <f t="array" ref="I14" xml:space="preserve"> IF(I$4&lt;&gt;$E14, MID($D14,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J14" s="47" t="str" cm="1">
+      <c r="J14" s="42" t="str" cm="1">
         <f t="array" ref="J14" xml:space="preserve"> IF(J$4&lt;&gt;$E14, MID($D14,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K14" s="47" t="str" cm="1">
+      <c r="K14" s="42" t="str" cm="1">
         <f t="array" ref="K14" xml:space="preserve"> IF(K$4&lt;&gt;$E14, MID($D14,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L14" s="47" t="str" cm="1">
+      <c r="L14" s="42" t="str" cm="1">
         <f t="array" ref="L14" xml:space="preserve"> IF(L$4&lt;&gt;$E14, MID($D14,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M14" s="47" t="str" cm="1">
+      <c r="M14" s="42" t="str" cm="1">
         <f t="array" ref="M14" xml:space="preserve"> IF(M$4&lt;&gt;$E14, MID($D14,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N14" s="47" t="str" cm="1">
+      <c r="N14" s="42" t="str" cm="1">
         <f t="array" ref="N14" xml:space="preserve"> IF(N$4&lt;&gt;$E14, MID($D14,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D14,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O14" s="49"/>
-      <c r="P14" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F14,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q14" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G14,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R14" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H14,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I14,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J14,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K14,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L14,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M14,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X14" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N14,".png")), "")</f>
+      <c r="O14" s="44"/>
+      <c r="P14" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q14" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R14" s="26" t="e" vm="6">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S14" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T14" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U14" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V14" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W14" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X14" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="27">
-        <f t="shared" si="0"/>
+      <c r="E15" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F15" s="47" t="str" cm="1">
+      <c r="F15" s="42" t="str" cm="1">
         <f t="array" ref="F15" xml:space="preserve"> IF(F$4&lt;&gt;$E15, MID($D15,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G15" s="47" t="str" cm="1">
+      <c r="G15" s="42" t="str" cm="1">
         <f t="array" ref="G15" xml:space="preserve"> IF(G$4&lt;&gt;$E15, MID($D15,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H15" s="47" t="str" cm="1">
+      <c r="H15" s="42" t="str" cm="1">
         <f t="array" ref="H15" xml:space="preserve"> IF(H$4&lt;&gt;$E15, MID($D15,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I15" s="47" t="str" cm="1">
+      <c r="I15" s="42" t="str" cm="1">
         <f t="array" ref="I15" xml:space="preserve"> IF(I$4&lt;&gt;$E15, MID($D15,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>backslash</v>
       </c>
-      <c r="J15" s="47" t="str" cm="1">
+      <c r="J15" s="42" t="str" cm="1">
         <f t="array" ref="J15" xml:space="preserve"> IF(J$4&lt;&gt;$E15, MID($D15,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K15" s="47" t="str" cm="1">
+      <c r="K15" s="42" t="str" cm="1">
         <f t="array" ref="K15" xml:space="preserve"> IF(K$4&lt;&gt;$E15, MID($D15,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L15" s="47" t="str" cm="1">
+      <c r="L15" s="42" t="str" cm="1">
         <f t="array" ref="L15" xml:space="preserve"> IF(L$4&lt;&gt;$E15, MID($D15,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M15" s="47" t="str" cm="1">
+      <c r="M15" s="42" t="str" cm="1">
         <f t="array" ref="M15" xml:space="preserve"> IF(M$4&lt;&gt;$E15, MID($D15,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N15" s="47" t="str" cm="1">
+      <c r="N15" s="42" t="str" cm="1">
         <f t="array" ref="N15" xml:space="preserve"> IF(N$4&lt;&gt;$E15, MID($D15,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D15,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O15" s="49"/>
-      <c r="P15" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F15,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q15" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G15,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R15" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H15,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S15" s="31" t="e" vm="14">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I15,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T15" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J15,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U15" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K15,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V15" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L15,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W15" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M15,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X15" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N15,".png")), "")</f>
+      <c r="O15" s="44"/>
+      <c r="P15" s="26" t="e" vm="9">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q15" s="26" t="e" vm="3">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R15" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S15" s="26" t="e" vm="14">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T15" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U15" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V15" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W15" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X15" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="2:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="27">
-        <f t="shared" si="0"/>
+      <c r="E16" s="23">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F16" s="47" t="str" cm="1">
+      <c r="F16" s="42" t="str" cm="1">
         <f t="array" ref="F16" xml:space="preserve"> IF(F$4&lt;&gt;$E16, MID($D16,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="G16" s="47" t="str" cm="1">
+      <c r="G16" s="42" t="str" cm="1">
         <f t="array" ref="G16" xml:space="preserve"> IF(G$4&lt;&gt;$E16, MID($D16,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H16" s="47" t="str" cm="1">
+      <c r="H16" s="42" t="str" cm="1">
         <f t="array" ref="H16" xml:space="preserve"> IF(H$4&lt;&gt;$E16, MID($D16,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="I16" s="47" t="str" cm="1">
+      <c r="I16" s="42" t="str" cm="1">
         <f t="array" ref="I16" xml:space="preserve"> IF(I$4&lt;&gt;$E16, MID($D16,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J16" s="47" t="str" cm="1">
+      <c r="J16" s="42" t="str" cm="1">
         <f t="array" ref="J16" xml:space="preserve"> IF(J$4&lt;&gt;$E16, MID($D16,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="K16" s="47" t="str" cm="1">
+      <c r="K16" s="42" t="str" cm="1">
         <f t="array" ref="K16" xml:space="preserve"> IF(K$4&lt;&gt;$E16, MID($D16,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>backslash</v>
       </c>
-      <c r="L16" s="47" t="str" cm="1">
+      <c r="L16" s="42" t="str" cm="1">
         <f t="array" ref="L16" xml:space="preserve"> IF(L$4&lt;&gt;$E16, MID($D16,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M16" s="47" t="str" cm="1">
+      <c r="M16" s="42" t="str" cm="1">
         <f t="array" ref="M16" xml:space="preserve"> IF(M$4&lt;&gt;$E16, MID($D16,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N16" s="47" t="str" cm="1">
+      <c r="N16" s="42" t="str" cm="1">
         <f t="array" ref="N16" xml:space="preserve"> IF(N$4&lt;&gt;$E16, MID($D16,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D16,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O16" s="49"/>
-      <c r="P16" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q16" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R16" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S16" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T16" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U16" s="31" t="e" vm="14">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K16,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V16" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L16,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W16" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M16,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X16" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N16,".png")), "")</f>
+      <c r="O16" s="44"/>
+      <c r="P16" s="26" t="e" vm="8">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q16" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R16" s="26" t="e" vm="11">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S16" s="26" t="e" vm="4">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T16" s="26" t="e" vm="5">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U16" s="26" t="e" vm="14">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V16" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W16" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X16" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="27">
-        <f t="shared" si="0"/>
+      <c r="E17" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F17" s="47" t="str" cm="1">
+      <c r="F17" s="42" t="str" cm="1">
         <f t="array" ref="F17" xml:space="preserve"> IF(F$4&lt;&gt;$E17, MID($D17,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="G17" s="47" t="str" cm="1">
+      <c r="G17" s="42" t="str" cm="1">
         <f t="array" ref="G17" xml:space="preserve"> IF(G$4&lt;&gt;$E17, MID($D17,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H17" s="47" t="str" cm="1">
+      <c r="H17" s="42" t="str" cm="1">
         <f t="array" ref="H17" xml:space="preserve"> IF(H$4&lt;&gt;$E17, MID($D17,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="I17" s="47" t="str" cm="1">
+      <c r="I17" s="42" t="str" cm="1">
         <f t="array" ref="I17" xml:space="preserve"> IF(I$4&lt;&gt;$E17, MID($D17,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>rbracket</v>
       </c>
-      <c r="J17" s="47" t="str" cm="1">
+      <c r="J17" s="42" t="str" cm="1">
         <f t="array" ref="J17" xml:space="preserve"> IF(J$4&lt;&gt;$E17, MID($D17,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K17" s="47" t="str" cm="1">
+      <c r="K17" s="42" t="str" cm="1">
         <f t="array" ref="K17" xml:space="preserve"> IF(K$4&lt;&gt;$E17, MID($D17,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L17" s="47" t="str" cm="1">
+      <c r="L17" s="42" t="str" cm="1">
         <f t="array" ref="L17" xml:space="preserve"> IF(L$4&lt;&gt;$E17, MID($D17,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M17" s="47" t="str" cm="1">
+      <c r="M17" s="42" t="str" cm="1">
         <f t="array" ref="M17" xml:space="preserve"> IF(M$4&lt;&gt;$E17, MID($D17,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N17" s="47" t="str" cm="1">
+      <c r="N17" s="42" t="str" cm="1">
         <f t="array" ref="N17" xml:space="preserve"> IF(N$4&lt;&gt;$E17, MID($D17,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D17,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O17" s="49"/>
-      <c r="P17" s="31" t="e" vm="15">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F17,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q17" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G17,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R17" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H17,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S17" s="31" t="e" vm="17">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I17,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T17" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J17,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U17" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K17,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V17" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L17,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W17" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M17,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X17" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N17,".png")), "")</f>
+      <c r="O17" s="44"/>
+      <c r="P17" s="26" t="e" vm="15">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q17" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R17" s="26" t="e" vm="16">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S17" s="26" t="e" vm="17">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T17" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U17" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V17" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W17" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X17" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="27">
-        <f t="shared" si="0"/>
+      <c r="E18" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F18" s="47" t="str" cm="1">
+      <c r="F18" s="42" t="str" cm="1">
         <f t="array" ref="F18" xml:space="preserve"> IF(F$4&lt;&gt;$E18, MID($D18,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G18" s="47" t="str" cm="1">
+      <c r="G18" s="42" t="str" cm="1">
         <f t="array" ref="G18" xml:space="preserve"> IF(G$4&lt;&gt;$E18, MID($D18,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H18" s="47" t="str" cm="1">
+      <c r="H18" s="42" t="str" cm="1">
         <f t="array" ref="H18" xml:space="preserve"> IF(H$4&lt;&gt;$E18, MID($D18,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I18" s="47" t="str" cm="1">
+      <c r="I18" s="42" t="str" cm="1">
         <f t="array" ref="I18" xml:space="preserve"> IF(I$4&lt;&gt;$E18, MID($D18,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="J18" s="47" t="str" cm="1">
+      <c r="J18" s="42" t="str" cm="1">
         <f t="array" ref="J18" xml:space="preserve"> IF(J$4&lt;&gt;$E18, MID($D18,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K18" s="47" t="str" cm="1">
+      <c r="K18" s="42" t="str" cm="1">
         <f t="array" ref="K18" xml:space="preserve"> IF(K$4&lt;&gt;$E18, MID($D18,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L18" s="47" t="str" cm="1">
+      <c r="L18" s="42" t="str" cm="1">
         <f t="array" ref="L18" xml:space="preserve"> IF(L$4&lt;&gt;$E18, MID($D18,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M18" s="47" t="str" cm="1">
+      <c r="M18" s="42" t="str" cm="1">
         <f t="array" ref="M18" xml:space="preserve"> IF(M$4&lt;&gt;$E18, MID($D18,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N18" s="47" t="str" cm="1">
+      <c r="N18" s="42" t="str" cm="1">
         <f t="array" ref="N18" xml:space="preserve"> IF(N$4&lt;&gt;$E18, MID($D18,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D18,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O18" s="49"/>
-      <c r="P18" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F18,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q18" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G18,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R18" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H18,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S18" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I18,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T18" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J18,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U18" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K18,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V18" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L18,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W18" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M18,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X18" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N18,".png")), "")</f>
+      <c r="O18" s="44"/>
+      <c r="P18" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q18" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R18" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S18" s="26" t="e" vm="6">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T18" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U18" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V18" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W18" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X18" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="27">
-        <f t="shared" si="0"/>
+      <c r="E19" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F19" s="47" t="str" cm="1">
+      <c r="F19" s="42" t="str" cm="1">
         <f t="array" ref="F19" xml:space="preserve"> IF(F$4&lt;&gt;$E19, MID($D19,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="G19" s="47" t="str" cm="1">
+      <c r="G19" s="42" t="str" cm="1">
         <f t="array" ref="G19" xml:space="preserve"> IF(G$4&lt;&gt;$E19, MID($D19,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H19" s="47" t="str" cm="1">
+      <c r="H19" s="42" t="str" cm="1">
         <f t="array" ref="H19" xml:space="preserve"> IF(H$4&lt;&gt;$E19, MID($D19,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I19" s="47" t="str" cm="1">
+      <c r="I19" s="42" t="str" cm="1">
         <f t="array" ref="I19" xml:space="preserve"> IF(I$4&lt;&gt;$E19, MID($D19,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="J19" s="47" t="str" cm="1">
+      <c r="J19" s="42" t="str" cm="1">
         <f t="array" ref="J19" xml:space="preserve"> IF(J$4&lt;&gt;$E19, MID($D19,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K19" s="47" t="str" cm="1">
+      <c r="K19" s="42" t="str" cm="1">
         <f t="array" ref="K19" xml:space="preserve"> IF(K$4&lt;&gt;$E19, MID($D19,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L19" s="47" t="str" cm="1">
+      <c r="L19" s="42" t="str" cm="1">
         <f t="array" ref="L19" xml:space="preserve"> IF(L$4&lt;&gt;$E19, MID($D19,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M19" s="47" t="str" cm="1">
+      <c r="M19" s="42" t="str" cm="1">
         <f t="array" ref="M19" xml:space="preserve"> IF(M$4&lt;&gt;$E19, MID($D19,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N19" s="47" t="str" cm="1">
+      <c r="N19" s="42" t="str" cm="1">
         <f t="array" ref="N19" xml:space="preserve"> IF(N$4&lt;&gt;$E19, MID($D19,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D19,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O19" s="49"/>
-      <c r="P19" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F19,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q19" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G19,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R19" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H19,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S19" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I19,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T19" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J19,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U19" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K19,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V19" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L19,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W19" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M19,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X19" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N19,".png")), "")</f>
+      <c r="O19" s="44"/>
+      <c r="P19" s="26" t="e" vm="16">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q19" s="26" t="e" vm="3">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R19" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S19" s="26" t="e" vm="10">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T19" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U19" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V19" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W19" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X19" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F20" s="47" t="str" cm="1">
+      <c r="C20" s="27"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F20" s="42" t="str" cm="1">
         <f t="array" ref="F20" xml:space="preserve"> IF(F$4&lt;&gt;$E20, MID($D20,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G20" s="47" t="str" cm="1">
+      <c r="G20" s="42" t="str" cm="1">
         <f t="array" ref="G20" xml:space="preserve"> IF(G$4&lt;&gt;$E20, MID($D20,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H20" s="47" t="str" cm="1">
+      <c r="H20" s="42" t="str" cm="1">
         <f t="array" ref="H20" xml:space="preserve"> IF(H$4&lt;&gt;$E20, MID($D20,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I20" s="47" t="str" cm="1">
+      <c r="I20" s="42" t="str" cm="1">
         <f t="array" ref="I20" xml:space="preserve"> IF(I$4&lt;&gt;$E20, MID($D20,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J20" s="47" t="str" cm="1">
+      <c r="J20" s="42" t="str" cm="1">
         <f t="array" ref="J20" xml:space="preserve"> IF(J$4&lt;&gt;$E20, MID($D20,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K20" s="47" t="str" cm="1">
+      <c r="K20" s="42" t="str" cm="1">
         <f t="array" ref="K20" xml:space="preserve"> IF(K$4&lt;&gt;$E20, MID($D20,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L20" s="47" t="str" cm="1">
+      <c r="L20" s="42" t="str" cm="1">
         <f t="array" ref="L20" xml:space="preserve"> IF(L$4&lt;&gt;$E20, MID($D20,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M20" s="47" t="str" cm="1">
+      <c r="M20" s="42" t="str" cm="1">
         <f t="array" ref="M20" xml:space="preserve"> IF(M$4&lt;&gt;$E20, MID($D20,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N20" s="47" t="str" cm="1">
+      <c r="N20" s="42" t="str" cm="1">
         <f t="array" ref="N20" xml:space="preserve"> IF(N$4&lt;&gt;$E20, MID($D20,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D20,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O20" s="49"/>
-      <c r="P20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M20,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X20" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N20,".png")), "")</f>
+      <c r="O20" s="44"/>
+      <c r="P20" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q20" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R20" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S20" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T20" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U20" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V20" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W20" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X20" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="27">
-        <f t="shared" si="0"/>
+      <c r="E21" s="23">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F21" s="47" t="str" cm="1">
+      <c r="F21" s="42" t="str" cm="1">
         <f t="array" ref="F21" xml:space="preserve"> IF(F$4&lt;&gt;$E21, MID($D21,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G21" s="47" t="str" cm="1">
+      <c r="G21" s="42" t="str" cm="1">
         <f t="array" ref="G21" xml:space="preserve"> IF(G$4&lt;&gt;$E21, MID($D21,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="H21" s="47" t="str" cm="1">
+      <c r="H21" s="42" t="str" cm="1">
         <f t="array" ref="H21" xml:space="preserve"> IF(H$4&lt;&gt;$E21, MID($D21,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>lbracket</v>
       </c>
-      <c r="I21" s="47" t="str" cm="1">
+      <c r="I21" s="42" t="str" cm="1">
         <f t="array" ref="I21" xml:space="preserve"> IF(I$4&lt;&gt;$E21, MID($D21,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J21" s="47" t="str" cm="1">
+      <c r="J21" s="42" t="str" cm="1">
         <f t="array" ref="J21" xml:space="preserve"> IF(J$4&lt;&gt;$E21, MID($D21,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K21" s="47" t="str" cm="1">
+      <c r="K21" s="42" t="str" cm="1">
         <f t="array" ref="K21" xml:space="preserve"> IF(K$4&lt;&gt;$E21, MID($D21,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L21" s="47" t="str" cm="1">
+      <c r="L21" s="42" t="str" cm="1">
         <f t="array" ref="L21" xml:space="preserve"> IF(L$4&lt;&gt;$E21, MID($D21,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M21" s="47" t="str" cm="1">
+      <c r="M21" s="42" t="str" cm="1">
         <f t="array" ref="M21" xml:space="preserve"> IF(M$4&lt;&gt;$E21, MID($D21,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N21" s="47" t="str" cm="1">
+      <c r="N21" s="42" t="str" cm="1">
         <f t="array" ref="N21" xml:space="preserve"> IF(N$4&lt;&gt;$E21, MID($D21,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D21,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O21" s="49"/>
-      <c r="P21" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F21,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q21" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G21,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R21" s="31" t="e" vm="18">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H21,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I21,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J21,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K21,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L21,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M21,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X21" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N21,".png")), "")</f>
+      <c r="O21" s="44"/>
+      <c r="P21" s="26" t="e" vm="2">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q21" s="26" t="e" vm="7">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R21" s="26" t="e" vm="18">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S21" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T21" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U21" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V21" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W21" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X21" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="27">
-        <f t="shared" si="0"/>
+      <c r="E22" s="23">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F22" s="47" t="str" cm="1">
+      <c r="F22" s="42" t="str" cm="1">
         <f t="array" ref="F22" xml:space="preserve"> IF(F$4&lt;&gt;$E22, MID($D22,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="G22" s="47" t="str" cm="1">
+      <c r="G22" s="42" t="str" cm="1">
         <f t="array" ref="G22" xml:space="preserve"> IF(G$4&lt;&gt;$E22, MID($D22,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="H22" s="47" t="str" cm="1">
+      <c r="H22" s="42" t="str" cm="1">
         <f t="array" ref="H22" xml:space="preserve"> IF(H$4&lt;&gt;$E22, MID($D22,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="I22" s="47" t="str" cm="1">
+      <c r="I22" s="42" t="str" cm="1">
         <f t="array" ref="I22" xml:space="preserve"> IF(I$4&lt;&gt;$E22, MID($D22,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="J22" s="47" t="str" cm="1">
+      <c r="J22" s="42" t="str" cm="1">
         <f t="array" ref="J22" xml:space="preserve"> IF(J$4&lt;&gt;$E22, MID($D22,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="K22" s="47" t="str" cm="1">
+      <c r="K22" s="42" t="str" cm="1">
         <f t="array" ref="K22" xml:space="preserve"> IF(K$4&lt;&gt;$E22, MID($D22,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="L22" s="47" t="str" cm="1">
+      <c r="L22" s="42" t="str" cm="1">
         <f t="array" ref="L22" xml:space="preserve"> IF(L$4&lt;&gt;$E22, MID($D22,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M22" s="47" t="str" cm="1">
+      <c r="M22" s="42" t="str" cm="1">
         <f t="array" ref="M22" xml:space="preserve"> IF(M$4&lt;&gt;$E22, MID($D22,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N22" s="47" t="str" cm="1">
+      <c r="N22" s="42" t="str" cm="1">
         <f t="array" ref="N22" xml:space="preserve"> IF(N$4&lt;&gt;$E22, MID($D22,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D22,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O22" s="49"/>
-      <c r="P22" s="31" t="e" vm="15">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q22" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R22" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S22" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T22" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U22" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K22,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V22" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L22,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W22" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M22,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X22" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N22,".png")), "")</f>
+      <c r="O22" s="44"/>
+      <c r="P22" s="26" t="e" vm="15">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q22" s="26" t="e" vm="12">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R22" s="26" t="e" vm="2">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S22" s="26" t="e" vm="3">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T22" s="26" t="e" vm="4">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U22" s="26" t="e" vm="13">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V22" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W22" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X22" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="27">
-        <f t="shared" si="0"/>
+      <c r="E23" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F23" s="47" t="str" cm="1">
+      <c r="F23" s="42" t="str" cm="1">
         <f t="array" ref="F23" xml:space="preserve"> IF(F$4&lt;&gt;$E23, MID($D23,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="G23" s="47" t="str" cm="1">
+      <c r="G23" s="42" t="str" cm="1">
         <f t="array" ref="G23" xml:space="preserve"> IF(G$4&lt;&gt;$E23, MID($D23,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H23" s="47" t="str" cm="1">
+      <c r="H23" s="42" t="str" cm="1">
         <f t="array" ref="H23" xml:space="preserve"> IF(H$4&lt;&gt;$E23, MID($D23,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="I23" s="47" t="str" cm="1">
+      <c r="I23" s="42" t="str" cm="1">
         <f t="array" ref="I23" xml:space="preserve"> IF(I$4&lt;&gt;$E23, MID($D23,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="J23" s="47" t="str" cm="1">
+      <c r="J23" s="42" t="str" cm="1">
         <f t="array" ref="J23" xml:space="preserve"> IF(J$4&lt;&gt;$E23, MID($D23,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K23" s="47" t="str" cm="1">
+      <c r="K23" s="42" t="str" cm="1">
         <f t="array" ref="K23" xml:space="preserve"> IF(K$4&lt;&gt;$E23, MID($D23,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L23" s="47" t="str" cm="1">
+      <c r="L23" s="42" t="str" cm="1">
         <f t="array" ref="L23" xml:space="preserve"> IF(L$4&lt;&gt;$E23, MID($D23,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M23" s="47" t="str" cm="1">
+      <c r="M23" s="42" t="str" cm="1">
         <f t="array" ref="M23" xml:space="preserve"> IF(M$4&lt;&gt;$E23, MID($D23,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N23" s="47" t="str" cm="1">
+      <c r="N23" s="42" t="str" cm="1">
         <f t="array" ref="N23" xml:space="preserve"> IF(N$4&lt;&gt;$E23, MID($D23,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D23,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O23" s="49"/>
-      <c r="P23" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F23,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q23" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G23,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R23" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H23,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S23" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I23,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T23" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J23,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U23" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K23,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V23" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L23,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W23" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M23,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X23" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N23,".png")), "")</f>
+      <c r="O23" s="44"/>
+      <c r="P23" s="26" t="e" vm="16">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q23" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R23" s="26" t="e" vm="11">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S23" s="26" t="e" vm="10">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T23" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U23" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V23" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W23" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X23" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="27">
-        <f t="shared" si="0"/>
+      <c r="E24" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F24" s="47" t="str" cm="1">
+      <c r="F24" s="42" t="str" cm="1">
         <f t="array" ref="F24" xml:space="preserve"> IF(F$4&lt;&gt;$E24, MID($D24,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="G24" s="47" t="str" cm="1">
+      <c r="G24" s="42" t="str" cm="1">
         <f t="array" ref="G24" xml:space="preserve"> IF(G$4&lt;&gt;$E24, MID($D24,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H24" s="47" t="str" cm="1">
+      <c r="H24" s="42" t="str" cm="1">
         <f t="array" ref="H24" xml:space="preserve"> IF(H$4&lt;&gt;$E24, MID($D24,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I24" s="47" t="str" cm="1">
+      <c r="I24" s="42" t="str" cm="1">
         <f t="array" ref="I24" xml:space="preserve"> IF(I$4&lt;&gt;$E24, MID($D24,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J24" s="47" t="str" cm="1">
+      <c r="J24" s="42" t="str" cm="1">
         <f t="array" ref="J24" xml:space="preserve"> IF(J$4&lt;&gt;$E24, MID($D24,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="K24" s="47" t="str" cm="1">
+      <c r="K24" s="42" t="str" cm="1">
         <f t="array" ref="K24" xml:space="preserve"> IF(K$4&lt;&gt;$E24, MID($D24,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L24" s="47" t="str" cm="1">
+      <c r="L24" s="42" t="str" cm="1">
         <f t="array" ref="L24" xml:space="preserve"> IF(L$4&lt;&gt;$E24, MID($D24,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M24" s="47" t="str" cm="1">
+      <c r="M24" s="42" t="str" cm="1">
         <f t="array" ref="M24" xml:space="preserve"> IF(M$4&lt;&gt;$E24, MID($D24,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N24" s="47" t="str" cm="1">
+      <c r="N24" s="42" t="str" cm="1">
         <f t="array" ref="N24" xml:space="preserve"> IF(N$4&lt;&gt;$E24, MID($D24,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D24,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O24" s="49"/>
-      <c r="P24" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F24,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q24" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G24,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R24" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H24,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S24" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I24,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T24" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J24,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U24" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K24,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V24" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L24,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W24" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M24,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X24" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N24,".png")), "")</f>
+      <c r="O24" s="44"/>
+      <c r="P24" s="26" t="e" vm="8">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q24" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R24" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S24" s="26" t="e" vm="5">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T24" s="26" t="e" vm="6">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U24" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V24" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W24" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X24" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="27">
-        <f t="shared" si="0"/>
+      <c r="E25" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F25" s="47" t="str" cm="1">
+      <c r="F25" s="42" t="str" cm="1">
         <f t="array" ref="F25" xml:space="preserve"> IF(F$4&lt;&gt;$E25, MID($D25,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>b</v>
       </c>
-      <c r="G25" s="47" t="str" cm="1">
+      <c r="G25" s="42" t="str" cm="1">
         <f t="array" ref="G25" xml:space="preserve"> IF(G$4&lt;&gt;$E25, MID($D25,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H25" s="47" t="str" cm="1">
+      <c r="H25" s="42" t="str" cm="1">
         <f t="array" ref="H25" xml:space="preserve"> IF(H$4&lt;&gt;$E25, MID($D25,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I25" s="47" t="str" cm="1">
+      <c r="I25" s="42" t="str" cm="1">
         <f t="array" ref="I25" xml:space="preserve"> IF(I$4&lt;&gt;$E25, MID($D25,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="J25" s="47" t="str" cm="1">
+      <c r="J25" s="42" t="str" cm="1">
         <f t="array" ref="J25" xml:space="preserve"> IF(J$4&lt;&gt;$E25, MID($D25,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K25" s="47" t="str" cm="1">
+      <c r="K25" s="42" t="str" cm="1">
         <f t="array" ref="K25" xml:space="preserve"> IF(K$4&lt;&gt;$E25, MID($D25,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L25" s="47" t="str" cm="1">
+      <c r="L25" s="42" t="str" cm="1">
         <f t="array" ref="L25" xml:space="preserve"> IF(L$4&lt;&gt;$E25, MID($D25,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M25" s="47" t="str" cm="1">
+      <c r="M25" s="42" t="str" cm="1">
         <f t="array" ref="M25" xml:space="preserve"> IF(M$4&lt;&gt;$E25, MID($D25,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N25" s="47" t="str" cm="1">
+      <c r="N25" s="42" t="str" cm="1">
         <f t="array" ref="N25" xml:space="preserve"> IF(N$4&lt;&gt;$E25, MID($D25,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D25,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O25" s="49"/>
-      <c r="P25" s="31" t="e" vm="19">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F25,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q25" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G25,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R25" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H25,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S25" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I25,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T25" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J25,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U25" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K25,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V25" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L25,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W25" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M25,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X25" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N25,".png")), "")</f>
+      <c r="O25" s="44"/>
+      <c r="P25" s="26" t="e" vm="19">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q25" s="26" t="e" vm="3">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R25" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S25" s="26" t="e" vm="13">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T25" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U25" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V25" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W25" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X25" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="27">
-        <f t="shared" si="0"/>
+      <c r="E26" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F26" s="47" t="str" cm="1">
+      <c r="F26" s="42" t="str" cm="1">
         <f t="array" ref="F26" xml:space="preserve"> IF(F$4&lt;&gt;$E26, MID($D26,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>j</v>
       </c>
-      <c r="G26" s="47" t="str" cm="1">
+      <c r="G26" s="42" t="str" cm="1">
         <f t="array" ref="G26" xml:space="preserve"> IF(G$4&lt;&gt;$E26, MID($D26,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H26" s="47" t="str" cm="1">
+      <c r="H26" s="42" t="str" cm="1">
         <f t="array" ref="H26" xml:space="preserve"> IF(H$4&lt;&gt;$E26, MID($D26,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>m</v>
       </c>
-      <c r="I26" s="47" t="str" cm="1">
+      <c r="I26" s="42" t="str" cm="1">
         <f t="array" ref="I26" xml:space="preserve"> IF(I$4&lt;&gt;$E26, MID($D26,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="J26" s="47" t="str" cm="1">
+      <c r="J26" s="42" t="str" cm="1">
         <f t="array" ref="J26" xml:space="preserve"> IF(J$4&lt;&gt;$E26, MID($D26,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K26" s="47" t="str" cm="1">
+      <c r="K26" s="42" t="str" cm="1">
         <f t="array" ref="K26" xml:space="preserve"> IF(K$4&lt;&gt;$E26, MID($D26,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L26" s="47" t="str" cm="1">
+      <c r="L26" s="42" t="str" cm="1">
         <f t="array" ref="L26" xml:space="preserve"> IF(L$4&lt;&gt;$E26, MID($D26,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M26" s="47" t="str" cm="1">
+      <c r="M26" s="42" t="str" cm="1">
         <f t="array" ref="M26" xml:space="preserve"> IF(M$4&lt;&gt;$E26, MID($D26,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N26" s="47" t="str" cm="1">
+      <c r="N26" s="42" t="str" cm="1">
         <f t="array" ref="N26" xml:space="preserve"> IF(N$4&lt;&gt;$E26, MID($D26,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D26,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O26" s="49"/>
-      <c r="P26" s="31" t="e" vm="20">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F26,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q26" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G26,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R26" s="31" t="e" vm="21">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H26,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S26" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I26,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T26" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J26,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U26" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K26,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V26" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L26,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W26" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M26,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X26" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N26,".png")), "")</f>
+      <c r="O26" s="44"/>
+      <c r="P26" s="26" t="e" vm="20">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q26" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R26" s="26" t="e" vm="21">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S26" s="26" t="e" vm="13">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T26" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U26" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V26" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W26" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X26" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="27">
-        <f t="shared" si="0"/>
+      <c r="E27" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F27" s="47" t="str" cm="1">
+      <c r="F27" s="42" t="str" cm="1">
         <f t="array" ref="F27" xml:space="preserve"> IF(F$4&lt;&gt;$E27, MID($D27,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="G27" s="47" t="str" cm="1">
+      <c r="G27" s="42" t="str" cm="1">
         <f t="array" ref="G27" xml:space="preserve"> IF(G$4&lt;&gt;$E27, MID($D27,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H27" s="47" t="str" cm="1">
+      <c r="H27" s="42" t="str" cm="1">
         <f t="array" ref="H27" xml:space="preserve"> IF(H$4&lt;&gt;$E27, MID($D27,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I27" s="47" t="str" cm="1">
+      <c r="I27" s="42" t="str" cm="1">
         <f t="array" ref="I27" xml:space="preserve"> IF(I$4&lt;&gt;$E27, MID($D27,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="J27" s="47" t="str" cm="1">
+      <c r="J27" s="42" t="str" cm="1">
         <f t="array" ref="J27" xml:space="preserve"> IF(J$4&lt;&gt;$E27, MID($D27,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K27" s="47" t="str" cm="1">
+      <c r="K27" s="42" t="str" cm="1">
         <f t="array" ref="K27" xml:space="preserve"> IF(K$4&lt;&gt;$E27, MID($D27,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L27" s="47" t="str" cm="1">
+      <c r="L27" s="42" t="str" cm="1">
         <f t="array" ref="L27" xml:space="preserve"> IF(L$4&lt;&gt;$E27, MID($D27,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M27" s="47" t="str" cm="1">
+      <c r="M27" s="42" t="str" cm="1">
         <f t="array" ref="M27" xml:space="preserve"> IF(M$4&lt;&gt;$E27, MID($D27,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N27" s="47" t="str" cm="1">
+      <c r="N27" s="42" t="str" cm="1">
         <f t="array" ref="N27" xml:space="preserve"> IF(N$4&lt;&gt;$E27, MID($D27,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D27,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O27" s="49"/>
-      <c r="P27" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F27,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q27" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G27,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R27" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H27,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S27" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I27,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T27" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J27,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U27" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K27,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V27" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L27,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W27" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M27,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X27" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N27,".png")), "")</f>
+      <c r="O27" s="44"/>
+      <c r="P27" s="26" t="e" vm="8">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q27" s="26" t="e" vm="3">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R27" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S27" s="26" t="e" vm="10">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T27" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U27" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V27" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W27" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X27" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F28" s="47" t="str" cm="1">
+      <c r="C28" s="27"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F28" s="42" t="str" cm="1">
         <f t="array" ref="F28" xml:space="preserve"> IF(F$4&lt;&gt;$E28, MID($D28,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G28" s="47" t="str" cm="1">
+      <c r="G28" s="42" t="str" cm="1">
         <f t="array" ref="G28" xml:space="preserve"> IF(G$4&lt;&gt;$E28, MID($D28,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H28" s="47" t="str" cm="1">
+      <c r="H28" s="42" t="str" cm="1">
         <f t="array" ref="H28" xml:space="preserve"> IF(H$4&lt;&gt;$E28, MID($D28,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I28" s="47" t="str" cm="1">
+      <c r="I28" s="42" t="str" cm="1">
         <f t="array" ref="I28" xml:space="preserve"> IF(I$4&lt;&gt;$E28, MID($D28,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J28" s="47" t="str" cm="1">
+      <c r="J28" s="42" t="str" cm="1">
         <f t="array" ref="J28" xml:space="preserve"> IF(J$4&lt;&gt;$E28, MID($D28,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K28" s="47" t="str" cm="1">
+      <c r="K28" s="42" t="str" cm="1">
         <f t="array" ref="K28" xml:space="preserve"> IF(K$4&lt;&gt;$E28, MID($D28,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L28" s="47" t="str" cm="1">
+      <c r="L28" s="42" t="str" cm="1">
         <f t="array" ref="L28" xml:space="preserve"> IF(L$4&lt;&gt;$E28, MID($D28,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M28" s="47" t="str" cm="1">
+      <c r="M28" s="42" t="str" cm="1">
         <f t="array" ref="M28" xml:space="preserve"> IF(M$4&lt;&gt;$E28, MID($D28,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N28" s="47" t="str" cm="1">
+      <c r="N28" s="42" t="str" cm="1">
         <f t="array" ref="N28" xml:space="preserve"> IF(N$4&lt;&gt;$E28, MID($D28,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D28,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O28" s="49"/>
-      <c r="P28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M28,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X28" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N28,".png")), "")</f>
+      <c r="O28" s="44"/>
+      <c r="P28" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q28" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R28" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S28" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T28" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U28" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V28" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W28" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X28" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="29"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F29" s="47" t="str" cm="1">
+      <c r="B29" s="24"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F29" s="42" t="str" cm="1">
         <f t="array" ref="F29" xml:space="preserve"> IF(F$4&lt;&gt;$E29, MID($D29,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G29" s="47" t="str" cm="1">
+      <c r="G29" s="42" t="str" cm="1">
         <f t="array" ref="G29" xml:space="preserve"> IF(G$4&lt;&gt;$E29, MID($D29,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H29" s="47" t="str" cm="1">
+      <c r="H29" s="42" t="str" cm="1">
         <f t="array" ref="H29" xml:space="preserve"> IF(H$4&lt;&gt;$E29, MID($D29,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I29" s="47" t="str" cm="1">
+      <c r="I29" s="42" t="str" cm="1">
         <f t="array" ref="I29" xml:space="preserve"> IF(I$4&lt;&gt;$E29, MID($D29,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J29" s="47" t="str" cm="1">
+      <c r="J29" s="42" t="str" cm="1">
         <f t="array" ref="J29" xml:space="preserve"> IF(J$4&lt;&gt;$E29, MID($D29,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K29" s="47" t="str" cm="1">
+      <c r="K29" s="42" t="str" cm="1">
         <f t="array" ref="K29" xml:space="preserve"> IF(K$4&lt;&gt;$E29, MID($D29,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L29" s="47" t="str" cm="1">
+      <c r="L29" s="42" t="str" cm="1">
         <f t="array" ref="L29" xml:space="preserve"> IF(L$4&lt;&gt;$E29, MID($D29,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M29" s="47" t="str" cm="1">
+      <c r="M29" s="42" t="str" cm="1">
         <f t="array" ref="M29" xml:space="preserve"> IF(M$4&lt;&gt;$E29, MID($D29,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N29" s="47" t="str" cm="1">
+      <c r="N29" s="42" t="str" cm="1">
         <f t="array" ref="N29" xml:space="preserve"> IF(N$4&lt;&gt;$E29, MID($D29,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D29,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O29" s="49"/>
-      <c r="P29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M29,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X29" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N29,".png")), "")</f>
+      <c r="O29" s="44"/>
+      <c r="P29" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q29" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R29" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S29" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T29" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U29" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V29" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W29" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X29" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="27">
-        <f t="shared" si="0"/>
+      <c r="E30" s="23">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="F30" s="47" t="str" cm="1">
+      <c r="F30" s="42" t="str" cm="1">
         <f t="array" ref="F30" xml:space="preserve"> IF(F$4&lt;&gt;$E30, MID($D30,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="G30" s="47" t="str" cm="1">
+      <c r="G30" s="42" t="str" cm="1">
         <f t="array" ref="G30" xml:space="preserve"> IF(G$4&lt;&gt;$E30, MID($D30,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="H30" s="47" t="str" cm="1">
+      <c r="H30" s="42" t="str" cm="1">
         <f t="array" ref="H30" xml:space="preserve"> IF(H$4&lt;&gt;$E30, MID($D30,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="I30" s="47" t="str" cm="1">
+      <c r="I30" s="42" t="str" cm="1">
         <f t="array" ref="I30" xml:space="preserve"> IF(I$4&lt;&gt;$E30, MID($D30,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="J30" s="47" t="str" cm="1">
+      <c r="J30" s="42" t="str" cm="1">
         <f t="array" ref="J30" xml:space="preserve"> IF(J$4&lt;&gt;$E30, MID($D30,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="K30" s="47" t="str" cm="1">
+      <c r="K30" s="42" t="str" cm="1">
         <f t="array" ref="K30" xml:space="preserve"> IF(K$4&lt;&gt;$E30, MID($D30,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="L30" s="47" t="str" cm="1">
+      <c r="L30" s="42" t="str" cm="1">
         <f t="array" ref="L30" xml:space="preserve"> IF(L$4&lt;&gt;$E30, MID($D30,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="M30" s="47" t="str" cm="1">
+      <c r="M30" s="42" t="str" cm="1">
         <f t="array" ref="M30" xml:space="preserve"> IF(M$4&lt;&gt;$E30, MID($D30,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N30" s="47" t="str" cm="1">
+      <c r="N30" s="42" t="str" cm="1">
         <f t="array" ref="N30" xml:space="preserve"> IF(N$4&lt;&gt;$E30, MID($D30,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D30,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O30" s="49"/>
-      <c r="P30" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q30" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R30" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S30" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T30" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U30" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V30" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L30,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W30" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M30,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X30" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N30,".png")), "")</f>
+      <c r="O30" s="44"/>
+      <c r="P30" s="26" t="e" vm="16">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q30" s="26" t="e" vm="12">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R30" s="26" t="e" vm="2">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S30" s="26" t="e" vm="3">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T30" s="26" t="e" vm="4">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U30" s="26" t="e" vm="5">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V30" s="26" t="e" vm="10">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W30" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X30" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="27">
-        <f t="shared" si="0"/>
+      <c r="E31" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F31" s="47" t="str" cm="1">
+      <c r="F31" s="42" t="str" cm="1">
         <f t="array" ref="F31" xml:space="preserve"> IF(F$4&lt;&gt;$E31, MID($D31,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G31" s="47" t="str" cm="1">
+      <c r="G31" s="42" t="str" cm="1">
         <f t="array" ref="G31" xml:space="preserve"> IF(G$4&lt;&gt;$E31, MID($D31,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H31" s="47" t="str" cm="1">
+      <c r="H31" s="42" t="str" cm="1">
         <f t="array" ref="H31" xml:space="preserve"> IF(H$4&lt;&gt;$E31, MID($D31,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="I31" s="47" t="str" cm="1">
+      <c r="I31" s="42" t="str" cm="1">
         <f t="array" ref="I31" xml:space="preserve"> IF(I$4&lt;&gt;$E31, MID($D31,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>rbracket</v>
       </c>
-      <c r="J31" s="47" t="str" cm="1">
+      <c r="J31" s="42" t="str" cm="1">
         <f t="array" ref="J31" xml:space="preserve"> IF(J$4&lt;&gt;$E31, MID($D31,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K31" s="47" t="str" cm="1">
+      <c r="K31" s="42" t="str" cm="1">
         <f t="array" ref="K31" xml:space="preserve"> IF(K$4&lt;&gt;$E31, MID($D31,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L31" s="47" t="str" cm="1">
+      <c r="L31" s="42" t="str" cm="1">
         <f t="array" ref="L31" xml:space="preserve"> IF(L$4&lt;&gt;$E31, MID($D31,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M31" s="47" t="str" cm="1">
+      <c r="M31" s="42" t="str" cm="1">
         <f t="array" ref="M31" xml:space="preserve"> IF(M$4&lt;&gt;$E31, MID($D31,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N31" s="47" t="str" cm="1">
+      <c r="N31" s="42" t="str" cm="1">
         <f t="array" ref="N31" xml:space="preserve"> IF(N$4&lt;&gt;$E31, MID($D31,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D31,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O31" s="49"/>
-      <c r="P31" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F31,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q31" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G31,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R31" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H31,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S31" s="31" t="e" vm="17">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I31,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T31" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J31,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U31" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K31,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V31" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L31,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W31" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M31,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X31" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N31,".png")), "")</f>
+      <c r="O31" s="44"/>
+      <c r="P31" s="26" t="e" vm="7">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q31" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R31" s="26" t="e" vm="16">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S31" s="26" t="e" vm="17">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T31" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U31" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V31" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W31" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X31" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="27">
-        <f t="shared" si="0"/>
+      <c r="E32" s="23">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F32" s="47" t="str" cm="1">
+      <c r="F32" s="42" t="str" cm="1">
         <f t="array" ref="F32" xml:space="preserve"> IF(F$4&lt;&gt;$E32, MID($D32,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G32" s="47" t="str" cm="1">
+      <c r="G32" s="42" t="str" cm="1">
         <f t="array" ref="G32" xml:space="preserve"> IF(G$4&lt;&gt;$E32, MID($D32,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H32" s="47" t="str" cm="1">
+      <c r="H32" s="42" t="str" cm="1">
         <f t="array" ref="H32" xml:space="preserve"> IF(H$4&lt;&gt;$E32, MID($D32,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="I32" s="47" t="str" cm="1">
+      <c r="I32" s="42" t="str" cm="1">
         <f t="array" ref="I32" xml:space="preserve"> IF(I$4&lt;&gt;$E32, MID($D32,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J32" s="47" t="str" cm="1">
+      <c r="J32" s="42" t="str" cm="1">
         <f t="array" ref="J32" xml:space="preserve"> IF(J$4&lt;&gt;$E32, MID($D32,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K32" s="47" t="str" cm="1">
+      <c r="K32" s="42" t="str" cm="1">
         <f t="array" ref="K32" xml:space="preserve"> IF(K$4&lt;&gt;$E32, MID($D32,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L32" s="47" t="str" cm="1">
+      <c r="L32" s="42" t="str" cm="1">
         <f t="array" ref="L32" xml:space="preserve"> IF(L$4&lt;&gt;$E32, MID($D32,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M32" s="47" t="str" cm="1">
+      <c r="M32" s="42" t="str" cm="1">
         <f t="array" ref="M32" xml:space="preserve"> IF(M$4&lt;&gt;$E32, MID($D32,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N32" s="47" t="str" cm="1">
+      <c r="N32" s="42" t="str" cm="1">
         <f t="array" ref="N32" xml:space="preserve"> IF(N$4&lt;&gt;$E32, MID($D32,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D32,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O32" s="49"/>
-      <c r="P32" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F32,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q32" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G32,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R32" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H32,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I32,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J32,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K32,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L32,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M32,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X32" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N32,".png")), "")</f>
+      <c r="O32" s="44"/>
+      <c r="P32" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q32" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R32" s="26" t="e" vm="6">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S32" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T32" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U32" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V32" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W32" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X32" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="27">
-        <f t="shared" si="0"/>
+      <c r="E33" s="23">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F33" s="47" t="str" cm="1">
+      <c r="F33" s="42" t="str" cm="1">
         <f t="array" ref="F33" xml:space="preserve"> IF(F$4&lt;&gt;$E33, MID($D33,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="G33" s="47" t="str" cm="1">
+      <c r="G33" s="42" t="str" cm="1">
         <f t="array" ref="G33" xml:space="preserve"> IF(G$4&lt;&gt;$E33, MID($D33,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H33" s="47" t="str" cm="1">
+      <c r="H33" s="42" t="str" cm="1">
         <f t="array" ref="H33" xml:space="preserve"> IF(H$4&lt;&gt;$E33, MID($D33,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="I33" s="47" t="str" cm="1">
+      <c r="I33" s="42" t="str" cm="1">
         <f t="array" ref="I33" xml:space="preserve"> IF(I$4&lt;&gt;$E33, MID($D33,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J33" s="47" t="str" cm="1">
+      <c r="J33" s="42" t="str" cm="1">
         <f t="array" ref="J33" xml:space="preserve"> IF(J$4&lt;&gt;$E33, MID($D33,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K33" s="47" t="str" cm="1">
+      <c r="K33" s="42" t="str" cm="1">
         <f t="array" ref="K33" xml:space="preserve"> IF(K$4&lt;&gt;$E33, MID($D33,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L33" s="47" t="str" cm="1">
+      <c r="L33" s="42" t="str" cm="1">
         <f t="array" ref="L33" xml:space="preserve"> IF(L$4&lt;&gt;$E33, MID($D33,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M33" s="47" t="str" cm="1">
+      <c r="M33" s="42" t="str" cm="1">
         <f t="array" ref="M33" xml:space="preserve"> IF(M$4&lt;&gt;$E33, MID($D33,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N33" s="47" t="str" cm="1">
+      <c r="N33" s="42" t="str" cm="1">
         <f t="array" ref="N33" xml:space="preserve"> IF(N$4&lt;&gt;$E33, MID($D33,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D33,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O33" s="49"/>
-      <c r="P33" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F33,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q33" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G33,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R33" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H33,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I33,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J33,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K33,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L33,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M33,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X33" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N33,".png")), "")</f>
+      <c r="O33" s="44"/>
+      <c r="P33" s="26" t="e" vm="8">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q33" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R33" s="26" t="e" vm="10">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S33" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T33" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U33" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V33" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W33" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X33" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="27">
-        <f t="shared" si="0"/>
+      <c r="E34" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F34" s="47" t="str" cm="1">
+      <c r="F34" s="42" t="str" cm="1">
         <f t="array" ref="F34" xml:space="preserve"> IF(F$4&lt;&gt;$E34, MID($D34,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="G34" s="47" t="str" cm="1">
+      <c r="G34" s="42" t="str" cm="1">
         <f t="array" ref="G34" xml:space="preserve"> IF(G$4&lt;&gt;$E34, MID($D34,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="H34" s="47" t="str" cm="1">
+      <c r="H34" s="42" t="str" cm="1">
         <f t="array" ref="H34" xml:space="preserve"> IF(H$4&lt;&gt;$E34, MID($D34,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I34" s="47" t="str" cm="1">
+      <c r="I34" s="42" t="str" cm="1">
         <f t="array" ref="I34" xml:space="preserve"> IF(I$4&lt;&gt;$E34, MID($D34,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="J34" s="47" t="str" cm="1">
+      <c r="J34" s="42" t="str" cm="1">
         <f t="array" ref="J34" xml:space="preserve"> IF(J$4&lt;&gt;$E34, MID($D34,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K34" s="47" t="str" cm="1">
+      <c r="K34" s="42" t="str" cm="1">
         <f t="array" ref="K34" xml:space="preserve"> IF(K$4&lt;&gt;$E34, MID($D34,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L34" s="47" t="str" cm="1">
+      <c r="L34" s="42" t="str" cm="1">
         <f t="array" ref="L34" xml:space="preserve"> IF(L$4&lt;&gt;$E34, MID($D34,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M34" s="47" t="str" cm="1">
+      <c r="M34" s="42" t="str" cm="1">
         <f t="array" ref="M34" xml:space="preserve"> IF(M$4&lt;&gt;$E34, MID($D34,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N34" s="47" t="str" cm="1">
+      <c r="N34" s="42" t="str" cm="1">
         <f t="array" ref="N34" xml:space="preserve"> IF(N$4&lt;&gt;$E34, MID($D34,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D34,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O34" s="49"/>
-      <c r="P34" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F34,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q34" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G34,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R34" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H34,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S34" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I34,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T34" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J34,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U34" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K34,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V34" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L34,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W34" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M34,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X34" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N34,".png")), "")</f>
+      <c r="O34" s="44"/>
+      <c r="P34" s="26" t="e" vm="9">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q34" s="26" t="e" vm="3">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R34" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S34" s="26" t="e" vm="13">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T34" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U34" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V34" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W34" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X34" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="C35" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="27">
-        <f t="shared" si="0"/>
+      <c r="E35" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F35" s="47" t="str" cm="1">
+      <c r="F35" s="42" t="str" cm="1">
         <f t="array" ref="F35" xml:space="preserve"> IF(F$4&lt;&gt;$E35, MID($D35,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="G35" s="47" t="str" cm="1">
+      <c r="G35" s="42" t="str" cm="1">
         <f t="array" ref="G35" xml:space="preserve"> IF(G$4&lt;&gt;$E35, MID($D35,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H35" s="47" t="str" cm="1">
+      <c r="H35" s="42" t="str" cm="1">
         <f t="array" ref="H35" xml:space="preserve"> IF(H$4&lt;&gt;$E35, MID($D35,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I35" s="47" t="str" cm="1">
+      <c r="I35" s="42" t="str" cm="1">
         <f t="array" ref="I35" xml:space="preserve"> IF(I$4&lt;&gt;$E35, MID($D35,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J35" s="47" t="str" cm="1">
+      <c r="J35" s="42" t="str" cm="1">
         <f t="array" ref="J35" xml:space="preserve"> IF(J$4&lt;&gt;$E35, MID($D35,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="K35" s="47" t="str" cm="1">
+      <c r="K35" s="42" t="str" cm="1">
         <f t="array" ref="K35" xml:space="preserve"> IF(K$4&lt;&gt;$E35, MID($D35,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L35" s="47" t="str" cm="1">
+      <c r="L35" s="42" t="str" cm="1">
         <f t="array" ref="L35" xml:space="preserve"> IF(L$4&lt;&gt;$E35, MID($D35,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M35" s="47" t="str" cm="1">
+      <c r="M35" s="42" t="str" cm="1">
         <f t="array" ref="M35" xml:space="preserve"> IF(M$4&lt;&gt;$E35, MID($D35,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N35" s="47" t="str" cm="1">
+      <c r="N35" s="42" t="str" cm="1">
         <f t="array" ref="N35" xml:space="preserve"> IF(N$4&lt;&gt;$E35, MID($D35,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D35,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O35" s="49"/>
-      <c r="P35" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F35,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q35" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G35,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R35" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H35,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S35" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I35,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T35" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J35,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U35" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K35,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V35" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L35,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W35" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M35,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X35" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N35,".png")), "")</f>
+      <c r="O35" s="44"/>
+      <c r="P35" s="26" t="e" vm="2">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q35" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R35" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S35" s="26" t="e" vm="5">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T35" s="26" t="e" vm="6">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U35" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V35" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W35" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X35" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="27">
-        <f t="shared" si="0"/>
+      <c r="E36" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F36" s="47" t="str" cm="1">
+      <c r="F36" s="42" t="str" cm="1">
         <f t="array" ref="F36" xml:space="preserve"> IF(F$4&lt;&gt;$E36, MID($D36,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>l</v>
       </c>
-      <c r="G36" s="47" t="str" cm="1">
+      <c r="G36" s="42" t="str" cm="1">
         <f t="array" ref="G36" xml:space="preserve"> IF(G$4&lt;&gt;$E36, MID($D36,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H36" s="47" t="str" cm="1">
+      <c r="H36" s="42" t="str" cm="1">
         <f t="array" ref="H36" xml:space="preserve"> IF(H$4&lt;&gt;$E36, MID($D36,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="I36" s="47" t="str" cm="1">
+      <c r="I36" s="42" t="str" cm="1">
         <f t="array" ref="I36" xml:space="preserve"> IF(I$4&lt;&gt;$E36, MID($D36,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>backslash</v>
       </c>
-      <c r="J36" s="47" t="str" cm="1">
+      <c r="J36" s="42" t="str" cm="1">
         <f t="array" ref="J36" xml:space="preserve"> IF(J$4&lt;&gt;$E36, MID($D36,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K36" s="47" t="str" cm="1">
+      <c r="K36" s="42" t="str" cm="1">
         <f t="array" ref="K36" xml:space="preserve"> IF(K$4&lt;&gt;$E36, MID($D36,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L36" s="47" t="str" cm="1">
+      <c r="L36" s="42" t="str" cm="1">
         <f t="array" ref="L36" xml:space="preserve"> IF(L$4&lt;&gt;$E36, MID($D36,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M36" s="47" t="str" cm="1">
+      <c r="M36" s="42" t="str" cm="1">
         <f t="array" ref="M36" xml:space="preserve"> IF(M$4&lt;&gt;$E36, MID($D36,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N36" s="47" t="str" cm="1">
+      <c r="N36" s="42" t="str" cm="1">
         <f t="array" ref="N36" xml:space="preserve"> IF(N$4&lt;&gt;$E36, MID($D36,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D36,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O36" s="49"/>
-      <c r="P36" s="31" t="e" vm="1">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F36,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q36" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G36,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R36" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H36,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S36" s="31" t="e" vm="14">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I36,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T36" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J36,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U36" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K36,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V36" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L36,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W36" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M36,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X36" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N36,".png")), "")</f>
+      <c r="O36" s="44"/>
+      <c r="P36" s="26" t="e" vm="1">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q36" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R36" s="26" t="e" vm="9">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S36" s="26" t="e" vm="14">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T36" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U36" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V36" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W36" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X36" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F37" s="47" t="str" cm="1">
+      <c r="C37" s="27"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F37" s="42" t="str" cm="1">
         <f t="array" ref="F37" xml:space="preserve"> IF(F$4&lt;&gt;$E37, MID($D37,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G37" s="47" t="str" cm="1">
+      <c r="G37" s="42" t="str" cm="1">
         <f t="array" ref="G37" xml:space="preserve"> IF(G$4&lt;&gt;$E37, MID($D37,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H37" s="47" t="str" cm="1">
+      <c r="H37" s="42" t="str" cm="1">
         <f t="array" ref="H37" xml:space="preserve"> IF(H$4&lt;&gt;$E37, MID($D37,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I37" s="47" t="str" cm="1">
+      <c r="I37" s="42" t="str" cm="1">
         <f t="array" ref="I37" xml:space="preserve"> IF(I$4&lt;&gt;$E37, MID($D37,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J37" s="47" t="str" cm="1">
+      <c r="J37" s="42" t="str" cm="1">
         <f t="array" ref="J37" xml:space="preserve"> IF(J$4&lt;&gt;$E37, MID($D37,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K37" s="47" t="str" cm="1">
+      <c r="K37" s="42" t="str" cm="1">
         <f t="array" ref="K37" xml:space="preserve"> IF(K$4&lt;&gt;$E37, MID($D37,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L37" s="47" t="str" cm="1">
+      <c r="L37" s="42" t="str" cm="1">
         <f t="array" ref="L37" xml:space="preserve"> IF(L$4&lt;&gt;$E37, MID($D37,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M37" s="47" t="str" cm="1">
+      <c r="M37" s="42" t="str" cm="1">
         <f t="array" ref="M37" xml:space="preserve"> IF(M$4&lt;&gt;$E37, MID($D37,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N37" s="47" t="str" cm="1">
+      <c r="N37" s="42" t="str" cm="1">
         <f t="array" ref="N37" xml:space="preserve"> IF(N$4&lt;&gt;$E37, MID($D37,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D37,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O37" s="49"/>
-      <c r="P37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M37,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X37" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N37,".png")), "")</f>
+      <c r="O37" s="44"/>
+      <c r="P37" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q37" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R37" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S37" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T37" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U37" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V37" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W37" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X37" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="E38" s="27">
-        <f t="shared" si="0"/>
+      <c r="E38" s="23">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F38" s="47" t="str" cm="1">
+      <c r="F38" s="42" t="str" cm="1">
         <f t="array" ref="F38" xml:space="preserve"> IF(F$4&lt;&gt;$E38, MID($D38,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G38" s="47" t="str" cm="1">
+      <c r="G38" s="42" t="str" cm="1">
         <f t="array" ref="G38" xml:space="preserve"> IF(G$4&lt;&gt;$E38, MID($D38,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>s</v>
       </c>
-      <c r="H38" s="47" t="str" cm="1">
+      <c r="H38" s="42" t="str" cm="1">
         <f t="array" ref="H38" xml:space="preserve"> IF(H$4&lt;&gt;$E38, MID($D38,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="I38" s="47" t="str" cm="1">
+      <c r="I38" s="42" t="str" cm="1">
         <f t="array" ref="I38" xml:space="preserve"> IF(I$4&lt;&gt;$E38, MID($D38,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="J38" s="47" t="str" cm="1">
+      <c r="J38" s="42" t="str" cm="1">
         <f t="array" ref="J38" xml:space="preserve"> IF(J$4&lt;&gt;$E38, MID($D38,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="K38" s="47" t="str" cm="1">
+      <c r="K38" s="42" t="str" cm="1">
         <f t="array" ref="K38" xml:space="preserve"> IF(K$4&lt;&gt;$E38, MID($D38,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="L38" s="47" t="str" cm="1">
+      <c r="L38" s="42" t="str" cm="1">
         <f t="array" ref="L38" xml:space="preserve"> IF(L$4&lt;&gt;$E38, MID($D38,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M38" s="47" t="str" cm="1">
+      <c r="M38" s="42" t="str" cm="1">
         <f t="array" ref="M38" xml:space="preserve"> IF(M$4&lt;&gt;$E38, MID($D38,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N38" s="47" t="str" cm="1">
+      <c r="N38" s="42" t="str" cm="1">
         <f t="array" ref="N38" xml:space="preserve"> IF(N$4&lt;&gt;$E38, MID($D38,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D38,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O38" s="49"/>
-      <c r="P38" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q38" s="31" t="e" vm="8">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R38" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S38" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T38" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U38" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K38,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V38" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L38,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W38" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M38,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X38" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N38,".png")), "")</f>
+      <c r="O38" s="44"/>
+      <c r="P38" s="26" t="e" vm="7">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q38" s="26" t="e" vm="8">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R38" s="26" t="e" vm="12">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S38" s="26" t="e" vm="9">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T38" s="26" t="e" vm="4">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U38" s="26" t="e" vm="10">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V38" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W38" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X38" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="E39" s="27">
-        <f t="shared" si="0"/>
+      <c r="E39" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F39" s="47" t="str" cm="1">
+      <c r="F39" s="42" t="str" cm="1">
         <f t="array" ref="F39" xml:space="preserve"> IF(F$4&lt;&gt;$E39, MID($D39,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>h</v>
       </c>
-      <c r="G39" s="47" t="str" cm="1">
+      <c r="G39" s="42" t="str" cm="1">
         <f t="array" ref="G39" xml:space="preserve"> IF(G$4&lt;&gt;$E39, MID($D39,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H39" s="47" t="str" cm="1">
+      <c r="H39" s="42" t="str" cm="1">
         <f t="array" ref="H39" xml:space="preserve"> IF(H$4&lt;&gt;$E39, MID($D39,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I39" s="47" t="str" cm="1">
+      <c r="I39" s="42" t="str" cm="1">
         <f t="array" ref="I39" xml:space="preserve"> IF(I$4&lt;&gt;$E39, MID($D39,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="J39" s="47" t="str" cm="1">
+      <c r="J39" s="42" t="str" cm="1">
         <f t="array" ref="J39" xml:space="preserve"> IF(J$4&lt;&gt;$E39, MID($D39,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="K39" s="47" t="str" cm="1">
+      <c r="K39" s="42" t="str" cm="1">
         <f t="array" ref="K39" xml:space="preserve"> IF(K$4&lt;&gt;$E39, MID($D39,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L39" s="47" t="str" cm="1">
+      <c r="L39" s="42" t="str" cm="1">
         <f t="array" ref="L39" xml:space="preserve"> IF(L$4&lt;&gt;$E39, MID($D39,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M39" s="47" t="str" cm="1">
+      <c r="M39" s="42" t="str" cm="1">
         <f t="array" ref="M39" xml:space="preserve"> IF(M$4&lt;&gt;$E39, MID($D39,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N39" s="47" t="str" cm="1">
+      <c r="N39" s="42" t="str" cm="1">
         <f t="array" ref="N39" xml:space="preserve"> IF(N$4&lt;&gt;$E39, MID($D39,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D39,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O39" s="49"/>
-      <c r="P39" s="31" t="e" vm="12">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F39,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q39" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G39,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R39" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H39,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S39" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I39,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T39" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J39,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U39" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K39,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V39" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L39,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W39" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M39,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X39" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N39,".png")), "")</f>
+      <c r="O39" s="44"/>
+      <c r="P39" s="26" t="e" vm="12">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q39" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R39" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S39" s="26" t="e" vm="5">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T39" s="26" t="e" vm="10">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U39" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V39" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W39" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X39" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E40" s="27">
-        <f t="shared" si="0"/>
+      <c r="E40" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F40" s="47" t="str" cm="1">
+      <c r="F40" s="42" t="str" cm="1">
         <f t="array" ref="F40" xml:space="preserve"> IF(F$4&lt;&gt;$E40, MID($D40,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>p</v>
       </c>
-      <c r="G40" s="47" t="str" cm="1">
+      <c r="G40" s="42" t="str" cm="1">
         <f t="array" ref="G40" xml:space="preserve"> IF(G$4&lt;&gt;$E40, MID($D40,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H40" s="47" t="str" cm="1">
+      <c r="H40" s="42" t="str" cm="1">
         <f t="array" ref="H40" xml:space="preserve"> IF(H$4&lt;&gt;$E40, MID($D40,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="I40" s="47" t="str" cm="1">
+      <c r="I40" s="42" t="str" cm="1">
         <f t="array" ref="I40" xml:space="preserve"> IF(I$4&lt;&gt;$E40, MID($D40,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>lbracket</v>
       </c>
-      <c r="J40" s="47" t="str" cm="1">
+      <c r="J40" s="42" t="str" cm="1">
         <f t="array" ref="J40" xml:space="preserve"> IF(J$4&lt;&gt;$E40, MID($D40,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K40" s="47" t="str" cm="1">
+      <c r="K40" s="42" t="str" cm="1">
         <f t="array" ref="K40" xml:space="preserve"> IF(K$4&lt;&gt;$E40, MID($D40,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L40" s="47" t="str" cm="1">
+      <c r="L40" s="42" t="str" cm="1">
         <f t="array" ref="L40" xml:space="preserve"> IF(L$4&lt;&gt;$E40, MID($D40,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M40" s="47" t="str" cm="1">
+      <c r="M40" s="42" t="str" cm="1">
         <f t="array" ref="M40" xml:space="preserve"> IF(M$4&lt;&gt;$E40, MID($D40,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N40" s="47" t="str" cm="1">
+      <c r="N40" s="42" t="str" cm="1">
         <f t="array" ref="N40" xml:space="preserve"> IF(N$4&lt;&gt;$E40, MID($D40,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D40,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O40" s="49"/>
-      <c r="P40" s="31" t="e" vm="15">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F40,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q40" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G40,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R40" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H40,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S40" s="31" t="e" vm="18">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I40,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T40" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J40,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U40" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K40,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V40" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L40,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W40" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M40,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X40" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N40,".png")), "")</f>
+      <c r="O40" s="44"/>
+      <c r="P40" s="26" t="e" vm="15">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q40" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R40" s="26" t="e" vm="7">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S40" s="26" t="e" vm="18">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T40" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U40" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V40" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W40" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X40" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="E41" s="27">
-        <f t="shared" si="0"/>
+      <c r="E41" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F41" s="47" t="str" cm="1">
+      <c r="F41" s="42" t="str" cm="1">
         <f t="array" ref="F41" xml:space="preserve"> IF(F$4&lt;&gt;$E41, MID($D41,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>t</v>
       </c>
-      <c r="G41" s="47" t="str" cm="1">
+      <c r="G41" s="42" t="str" cm="1">
         <f t="array" ref="G41" xml:space="preserve"> IF(G$4&lt;&gt;$E41, MID($D41,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="H41" s="47" t="str" cm="1">
+      <c r="H41" s="42" t="str" cm="1">
         <f t="array" ref="H41" xml:space="preserve"> IF(H$4&lt;&gt;$E41, MID($D41,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="I41" s="47" t="str" cm="1">
+      <c r="I41" s="42" t="str" cm="1">
         <f t="array" ref="I41" xml:space="preserve"> IF(I$4&lt;&gt;$E41, MID($D41,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>minus</v>
       </c>
-      <c r="J41" s="47" t="str" cm="1">
+      <c r="J41" s="42" t="str" cm="1">
         <f t="array" ref="J41" xml:space="preserve"> IF(J$4&lt;&gt;$E41, MID($D41,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K41" s="47" t="str" cm="1">
+      <c r="K41" s="42" t="str" cm="1">
         <f t="array" ref="K41" xml:space="preserve"> IF(K$4&lt;&gt;$E41, MID($D41,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L41" s="47" t="str" cm="1">
+      <c r="L41" s="42" t="str" cm="1">
         <f t="array" ref="L41" xml:space="preserve"> IF(L$4&lt;&gt;$E41, MID($D41,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M41" s="47" t="str" cm="1">
+      <c r="M41" s="42" t="str" cm="1">
         <f t="array" ref="M41" xml:space="preserve"> IF(M$4&lt;&gt;$E41, MID($D41,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N41" s="47" t="str" cm="1">
+      <c r="N41" s="42" t="str" cm="1">
         <f t="array" ref="N41" xml:space="preserve"> IF(N$4&lt;&gt;$E41, MID($D41,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D41,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O41" s="49"/>
-      <c r="P41" s="31" t="e" vm="7">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F41,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q41" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G41,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R41" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H41,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S41" s="31" t="e" vm="13">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I41,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T41" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J41,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U41" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K41,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V41" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L41,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W41" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M41,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X41" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N41,".png")), "")</f>
+      <c r="O41" s="44"/>
+      <c r="P41" s="26" t="e" vm="7">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q41" s="26" t="e" vm="11">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R41" s="26" t="e" vm="11">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S41" s="26" t="e" vm="13">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T41" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U41" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V41" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W41" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X41" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="27">
-        <f t="shared" si="0"/>
+      <c r="E42" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F42" s="47" t="str" cm="1">
+      <c r="F42" s="42" t="str" cm="1">
         <f t="array" ref="F42" xml:space="preserve"> IF(F$4&lt;&gt;$E42, MID($D42,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>g</v>
       </c>
-      <c r="G42" s="47" t="str" cm="1">
+      <c r="G42" s="42" t="str" cm="1">
         <f t="array" ref="G42" xml:space="preserve"> IF(G$4&lt;&gt;$E42, MID($D42,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>i</v>
       </c>
-      <c r="H42" s="47" t="str" cm="1">
+      <c r="H42" s="42" t="str" cm="1">
         <f t="array" ref="H42" xml:space="preserve"> IF(H$4&lt;&gt;$E42, MID($D42,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>o</v>
       </c>
-      <c r="I42" s="47" t="str" cm="1">
+      <c r="I42" s="42" t="str" cm="1">
         <f t="array" ref="I42" xml:space="preserve"> IF(I$4&lt;&gt;$E42, MID($D42,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="J42" s="47" t="str" cm="1">
+      <c r="J42" s="42" t="str" cm="1">
         <f t="array" ref="J42" xml:space="preserve"> IF(J$4&lt;&gt;$E42, MID($D42,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>rbracket</v>
       </c>
-      <c r="K42" s="47" t="str" cm="1">
+      <c r="K42" s="42" t="str" cm="1">
         <f t="array" ref="K42" xml:space="preserve"> IF(K$4&lt;&gt;$E42, MID($D42,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L42" s="47" t="str" cm="1">
+      <c r="L42" s="42" t="str" cm="1">
         <f t="array" ref="L42" xml:space="preserve"> IF(L$4&lt;&gt;$E42, MID($D42,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M42" s="47" t="str" cm="1">
+      <c r="M42" s="42" t="str" cm="1">
         <f t="array" ref="M42" xml:space="preserve"> IF(M$4&lt;&gt;$E42, MID($D42,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N42" s="47" t="str" cm="1">
+      <c r="N42" s="42" t="str" cm="1">
         <f t="array" ref="N42" xml:space="preserve"> IF(N$4&lt;&gt;$E42, MID($D42,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D42,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O42" s="49"/>
-      <c r="P42" s="31" t="e" vm="5">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F42,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q42" s="31" t="e" vm="2">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G42,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R42" s="31" t="e" vm="11">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H42,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S42" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I42,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T42" s="31" t="e" vm="17">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J42,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U42" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K42,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V42" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L42,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W42" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M42,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X42" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N42,".png")), "")</f>
+      <c r="O42" s="44"/>
+      <c r="P42" s="26" t="e" vm="5">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q42" s="26" t="e" vm="2">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R42" s="26" t="e" vm="11">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S42" s="26" t="e" vm="16">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T42" s="26" t="e" vm="17">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U42" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V42" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W42" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X42" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="D43" s="30" t="s">
+      <c r="D43" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="E43" s="27">
-        <f t="shared" si="0"/>
+      <c r="E43" s="23">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F43" s="47" t="str" cm="1">
+      <c r="F43" s="42" t="str" cm="1">
         <f t="array" ref="F43" xml:space="preserve"> IF(F$4&lt;&gt;$E43, MID($D43,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>b</v>
       </c>
-      <c r="G43" s="47" t="str" cm="1">
+      <c r="G43" s="42" t="str" cm="1">
         <f t="array" ref="G43" xml:space="preserve"> IF(G$4&lt;&gt;$E43, MID($D43,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H43" s="47" t="str" cm="1">
+      <c r="H43" s="42" t="str" cm="1">
         <f t="array" ref="H43" xml:space="preserve"> IF(H$4&lt;&gt;$E43, MID($D43,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="I43" s="47" t="str" cm="1">
+      <c r="I43" s="42" t="str" cm="1">
         <f t="array" ref="I43" xml:space="preserve"> IF(I$4&lt;&gt;$E43, MID($D43,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>slash</v>
       </c>
-      <c r="J43" s="47" t="str" cm="1">
+      <c r="J43" s="42" t="str" cm="1">
         <f t="array" ref="J43" xml:space="preserve"> IF(J$4&lt;&gt;$E43, MID($D43,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K43" s="47" t="str" cm="1">
+      <c r="K43" s="42" t="str" cm="1">
         <f t="array" ref="K43" xml:space="preserve"> IF(K$4&lt;&gt;$E43, MID($D43,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L43" s="47" t="str" cm="1">
+      <c r="L43" s="42" t="str" cm="1">
         <f t="array" ref="L43" xml:space="preserve"> IF(L$4&lt;&gt;$E43, MID($D43,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M43" s="47" t="str" cm="1">
+      <c r="M43" s="42" t="str" cm="1">
         <f t="array" ref="M43" xml:space="preserve"> IF(M$4&lt;&gt;$E43, MID($D43,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N43" s="47" t="str" cm="1">
+      <c r="N43" s="42" t="str" cm="1">
         <f t="array" ref="N43" xml:space="preserve"> IF(N$4&lt;&gt;$E43, MID($D43,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D43,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O43" s="49"/>
-      <c r="P43" s="31" t="e" vm="19">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F43,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q43" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G43,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R43" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H43,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S43" s="31" t="e" vm="6">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I43,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T43" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J43,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U43" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K43,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V43" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L43,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W43" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M43,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X43" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N43,".png")), "")</f>
+      <c r="O43" s="44"/>
+      <c r="P43" s="26" t="e" vm="19">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q43" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R43" s="26" t="e" vm="4">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S43" s="26" t="e" vm="6">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T43" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U43" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V43" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W43" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X43" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="27">
-        <f t="shared" si="0"/>
+      <c r="E44" s="23">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="F44" s="47" t="str" cm="1">
+      <c r="F44" s="42" t="str" cm="1">
         <f t="array" ref="F44" xml:space="preserve"> IF(F$4&lt;&gt;$E44, MID($D44,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>k</v>
       </c>
-      <c r="G44" s="47" t="str" cm="1">
+      <c r="G44" s="42" t="str" cm="1">
         <f t="array" ref="G44" xml:space="preserve"> IF(G$4&lt;&gt;$E44, MID($D44,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>u</v>
       </c>
-      <c r="H44" s="47" t="str" cm="1">
+      <c r="H44" s="42" t="str" cm="1">
         <f t="array" ref="H44" xml:space="preserve"> IF(H$4&lt;&gt;$E44, MID($D44,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>a</v>
       </c>
-      <c r="I44" s="47" t="str" cm="1">
+      <c r="I44" s="42" t="str" cm="1">
         <f t="array" ref="I44" xml:space="preserve"> IF(I$4&lt;&gt;$E44, MID($D44,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>n</v>
       </c>
-      <c r="J44" s="47" t="str" cm="1">
+      <c r="J44" s="42" t="str" cm="1">
         <f t="array" ref="J44" xml:space="preserve"> IF(J$4&lt;&gt;$E44, MID($D44,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v>semicolon</v>
       </c>
-      <c r="K44" s="47" t="str" cm="1">
+      <c r="K44" s="42" t="str" cm="1">
         <f t="array" ref="K44" xml:space="preserve"> IF(K$4&lt;&gt;$E44, MID($D44,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L44" s="47" t="str" cm="1">
+      <c r="L44" s="42" t="str" cm="1">
         <f t="array" ref="L44" xml:space="preserve"> IF(L$4&lt;&gt;$E44, MID($D44,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M44" s="47" t="str" cm="1">
+      <c r="M44" s="42" t="str" cm="1">
         <f t="array" ref="M44" xml:space="preserve"> IF(M$4&lt;&gt;$E44, MID($D44,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N44" s="47" t="str" cm="1">
+      <c r="N44" s="42" t="str" cm="1">
         <f t="array" ref="N44" xml:space="preserve"> IF(N$4&lt;&gt;$E44, MID($D44,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D44,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O44" s="49"/>
-      <c r="P44" s="31" t="e" vm="16">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F44,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q44" s="31" t="e" vm="9">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G44,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R44" s="31" t="e" vm="3">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H44,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S44" s="31" t="e" vm="4">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I44,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T44" s="31" t="e" vm="10">
-        <f xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J44,".png")), "")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U44" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K44,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V44" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L44,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W44" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M44,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X44" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N44,".png")), "")</f>
+      <c r="O44" s="44"/>
+      <c r="P44" s="26" t="e" vm="16">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q44" s="26" t="e" vm="9">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R44" s="26" t="e" vm="3">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S44" s="26" t="e" vm="4">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T44" s="26" t="e" vm="10">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U44" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V44" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W44" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X44" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="2:24" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="32"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F45" s="47" t="str" cm="1">
+      <c r="C45" s="27"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F45" s="42" t="str" cm="1">
         <f t="array" ref="F45" xml:space="preserve"> IF(F$4&lt;&gt;$E45, MID($D45,F$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,F$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="G45" s="47" t="str" cm="1">
+      <c r="G45" s="42" t="str" cm="1">
         <f t="array" ref="G45" xml:space="preserve"> IF(G$4&lt;&gt;$E45, MID($D45,G$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,G$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="H45" s="47" t="str" cm="1">
+      <c r="H45" s="42" t="str" cm="1">
         <f t="array" ref="H45" xml:space="preserve"> IF(H$4&lt;&gt;$E45, MID($D45,H$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,H$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="I45" s="47" t="str" cm="1">
+      <c r="I45" s="42" t="str" cm="1">
         <f t="array" ref="I45" xml:space="preserve"> IF(I$4&lt;&gt;$E45, MID($D45,I$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,I$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="J45" s="47" t="str" cm="1">
+      <c r="J45" s="42" t="str" cm="1">
         <f t="array" ref="J45" xml:space="preserve"> IF(J$4&lt;&gt;$E45, MID($D45,J$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,J$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="K45" s="47" t="str" cm="1">
+      <c r="K45" s="42" t="str" cm="1">
         <f t="array" ref="K45" xml:space="preserve"> IF(K$4&lt;&gt;$E45, MID($D45,K$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,K$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="L45" s="47" t="str" cm="1">
+      <c r="L45" s="42" t="str" cm="1">
         <f t="array" ref="L45" xml:space="preserve"> IF(L$4&lt;&gt;$E45, MID($D45,L$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,L$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="M45" s="47" t="str" cm="1">
+      <c r="M45" s="42" t="str" cm="1">
         <f t="array" ref="M45" xml:space="preserve"> IF(M$4&lt;&gt;$E45, MID($D45,M$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,M$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="N45" s="47" t="str" cm="1">
+      <c r="N45" s="42" t="str" cm="1">
         <f t="array" ref="N45" xml:space="preserve"> IF(N$4&lt;&gt;$E45, MID($D45,N$4,1), INDEX(音調表[Key], MATCH(TRUE, EXACT(MID($D45,N$4,1), 音調表!$B$3:$B$12),0)))</f>
         <v/>
       </c>
-      <c r="O45" s="49"/>
-      <c r="P45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,F45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="Q45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,G45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="R45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,H45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="S45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,I45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="T45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,J45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="U45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,K45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="V45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,L45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="W45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,M45,".png")), "")</f>
-        <v/>
-      </c>
-      <c r="X45" s="31" t="str">
-        <f ca="1" xml:space="preserve"> IFERROR( _xlfn.IMAGE(_xlfn.CONCAT($D$1,N45,".png")), "")</f>
+      <c r="O45" s="44"/>
+      <c r="P45" s="26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="Q45" s="26" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v/>
+      </c>
+      <c r="R45" s="26" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S45" s="26" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
+      </c>
+      <c r="T45" s="26" t="str">
+        <f t="shared" ca="1" si="6"/>
+        <v/>
+      </c>
+      <c r="U45" s="26" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v/>
+      </c>
+      <c r="V45" s="26" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v/>
+      </c>
+      <c r="W45" s="26" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="X45" s="26" t="str">
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
     </row>
@@ -10592,30 +10592,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34">
+      <c r="B3" s="29">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -10633,12 +10633,12 @@
       <c r="G3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="35">
+      <c r="B4" s="30">
         <v>2</v>
       </c>
       <c r="C4" s="8" t="s">
@@ -10656,12 +10656,12 @@
       <c r="G4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="32" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="34">
+      <c r="B5" s="29">
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -10679,12 +10679,12 @@
       <c r="G5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="35">
+      <c r="B6" s="30">
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -10693,7 +10693,7 @@
       <c r="D6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="41" t="s">
         <v>170</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -10702,12 +10702,12 @@
       <c r="G6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="32" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="34">
+      <c r="B7" s="29">
         <v>5</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -10725,12 +10725,12 @@
       <c r="G7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="31" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="35">
+      <c r="B8" s="30">
         <v>6</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -10748,12 +10748,12 @@
       <c r="G8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="32" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="34">
+      <c r="B9" s="29">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -10771,12 +10771,12 @@
       <c r="G9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="31" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="35">
+      <c r="B10" s="30">
         <v>8</v>
       </c>
       <c r="C10" s="8" t="s">
@@ -10785,7 +10785,7 @@
       <c r="D10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="41" t="s">
         <v>169</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -10794,12 +10794,12 @@
       <c r="G10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="32" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="34">
+      <c r="B11" s="29">
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -10815,28 +10815,28 @@
       <c r="G11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="36" t="s">
+      <c r="H11" s="31" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="42">
+      <c r="B12" s="37">
         <v>0</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44" t="s">
+      <c r="E12" s="39"/>
+      <c r="F12" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="40" t="s">
         <v>43</v>
       </c>
     </row>
